--- a/Planilhas/MONITORAMENTOS DE ALARMES COORDENACAO COR ABRIL-junho26 (consolidado).xlsx
+++ b/Planilhas/MONITORAMENTOS DE ALARMES COORDENACAO COR ABRIL-junho26 (consolidado).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repo\Ocorrencias_Espontaneas\Planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34DAD0B4-324E-45EB-8049-3536265DCF36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5835992C-D678-4934-B269-1D67EF746BA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="525" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9382" uniqueCount="2938">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9384" uniqueCount="2939">
   <si>
     <t>Data</t>
   </si>
@@ -8855,6 +8855,9 @@
   </si>
   <si>
     <t>BOULEVARD VINTE E OITO DE SETEMBRO - VILA ISABEL - ALT. Nº 277</t>
+  </si>
+  <si>
+    <t>AGOSTO</t>
   </si>
 </sst>
 </file>
@@ -8865,7 +8868,7 @@
     <numFmt numFmtId="164" formatCode="d/mmm"/>
     <numFmt numFmtId="165" formatCode="d\-mmm"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -9008,6 +9011,11 @@
       <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="6">
@@ -9600,7 +9608,9 @@
       <c r="M3" s="3" t="s">
         <v>2141</v>
       </c>
-      <c r="N3" s="2"/>
+      <c r="N3" s="3" t="s">
+        <v>2938</v>
+      </c>
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
@@ -9641,7 +9651,9 @@
       <c r="M4" s="9">
         <v>2530</v>
       </c>
-      <c r="N4" s="4"/>
+      <c r="N4" s="9">
+        <v>2470</v>
+      </c>
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
       <c r="Q4" s="4"/>
@@ -9686,7 +9698,9 @@
       <c r="M5" s="9">
         <v>367</v>
       </c>
-      <c r="N5" s="10"/>
+      <c r="N5" s="9">
+        <v>504</v>
+      </c>
       <c r="O5" s="10"/>
       <c r="P5" s="10"/>
       <c r="Q5" s="10"/>
@@ -9799,7 +9813,9 @@
       <c r="M8" s="3" t="s">
         <v>2141</v>
       </c>
-      <c r="N8" s="9"/>
+      <c r="N8" s="3" t="s">
+        <v>2938</v>
+      </c>
       <c r="O8" s="9"/>
       <c r="P8" s="9"/>
       <c r="Q8" s="9"/>
@@ -9849,7 +9865,10 @@
         <f>100%-M10</f>
         <v>0.85494071146245054</v>
       </c>
-      <c r="N9" s="9"/>
+      <c r="N9" s="16">
+        <f>100%-N10</f>
+        <v>0.79595141700404859</v>
+      </c>
       <c r="O9" s="9"/>
       <c r="P9" s="9"/>
       <c r="Q9" s="9"/>
@@ -9897,7 +9916,10 @@
         <f>M5/M4</f>
         <v>0.1450592885375494</v>
       </c>
-      <c r="N10" s="9"/>
+      <c r="N10" s="16">
+        <f>N5/N4</f>
+        <v>0.20404858299595141</v>
+      </c>
       <c r="O10" s="9"/>
       <c r="P10" s="9"/>
       <c r="Q10" s="9"/>
@@ -50411,6 +50433,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.51180555555555596" right="0.51180555555555596" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>

--- a/Planilhas/MONITORAMENTOS DE ALARMES COORDENACAO COR ABRIL-junho26 (consolidado).xlsx
+++ b/Planilhas/MONITORAMENTOS DE ALARMES COORDENACAO COR ABRIL-junho26 (consolidado).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repo\Ocorrencias_Espontaneas\Planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E612749E-5BAE-4640-9372-2564B8B5D0E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F602DE4-E89D-40B1-B6F9-31936ADFCCC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="525" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10864" uniqueCount="3341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10865" uniqueCount="3311">
   <si>
     <t>Data</t>
   </si>
@@ -8743,9 +8743,6 @@
     <t>AGOSTO</t>
   </si>
   <si>
-    <t>Matheus/Ricado/Jackson/Márcio</t>
-  </si>
-  <si>
     <t xml:space="preserve">Av. Brasil - Alt. Estr. Mal Alencastro - Sent. Centro - Deodoro </t>
   </si>
   <si>
@@ -8764,9 +8761,6 @@
     <t>Google Maps / Alarme HxGN / Tixxi Cam 147</t>
   </si>
   <si>
-    <t xml:space="preserve">Matheus/Ricardo/Maggessi </t>
-  </si>
-  <si>
     <t xml:space="preserve">Av. Brasil - Alt. Av. Brg. Trompowski - Sent. Z. Oeste - Maré </t>
   </si>
   <si>
@@ -8788,9 +8782,6 @@
     <t xml:space="preserve">R. Mena Barreto - Alt. R. Real Grandeza - Botafogo </t>
   </si>
   <si>
-    <t>Matheus/Ricardo/Maggesi</t>
-  </si>
-  <si>
     <t>Av. Pastor Martin Luther King - Alt. Av. Monsenhor Félix - Sent. Vicente de Carvalho - Irajá</t>
   </si>
   <si>
@@ -8803,9 +8794,6 @@
     <t xml:space="preserve">Av. das Américas - Alt. Est. BRT Bosque da Barra - Sent. São Conrado - Barra da Tijuca </t>
   </si>
   <si>
-    <t xml:space="preserve">Alex / Hugo / Felipe </t>
-  </si>
-  <si>
     <t>Google Maps / Alarme HxGN / Tixxi Cam 4226</t>
   </si>
   <si>
@@ -8869,15 +8857,9 @@
     <t>AC ON x CM</t>
   </si>
   <si>
-    <t>Maggessi / Vinicius / Diego</t>
-  </si>
-  <si>
     <t>ESTRADA DAS FURNAS - ALT. Nº 777 - ALTO DA BOA VISTA</t>
   </si>
   <si>
-    <t xml:space="preserve">Daniel / Hugo / Felipe </t>
-  </si>
-  <si>
     <t>AVENIDA BRASIL - ALT. BATAN - SENT. Z. OESTE - REALENGO</t>
   </si>
   <si>
@@ -8953,9 +8935,6 @@
     <t>Google Maps / Alarme HxGN / Tixxi Cam 4501</t>
   </si>
   <si>
-    <t>Márcio / Vinicius / Diego / Jackson</t>
-  </si>
-  <si>
     <t>Av. Infante Dom Henrique - Alt. Rua do Russel - Sent. Copacabana</t>
   </si>
   <si>
@@ -8980,9 +8959,6 @@
     <t>AVENIDA REI PELÉ - ALT. PASSARELA DO TREM - SENT. MEIER</t>
   </si>
   <si>
-    <t>Marcio / Jackson / Diego / Vinicius</t>
-  </si>
-  <si>
     <t>ESTRADA DOS BANDEIRANTES - ALT. R. ARUÁ - SENT. RECREIO - CURICICA</t>
   </si>
   <si>
@@ -9013,15 +8989,9 @@
     <t>Waze</t>
   </si>
   <si>
-    <t>Vitor / Carlos / Alex</t>
-  </si>
-  <si>
     <t>AVENIDA DAS AMÉRICAS - ALT. AV. GILKA MACHADO - SENT. SÃO CONRADO - RECREIO DOS BANDEIRANTES</t>
   </si>
   <si>
-    <t>Matheus/Ricardo/Jackson/Márcio</t>
-  </si>
-  <si>
     <t>Google Maps / Alarme HxGN / Tixxi Cam 3212</t>
   </si>
   <si>
@@ -9067,9 +9037,6 @@
     <t>Google Maps / Alarme HxGN / Tixxi Cam 392</t>
   </si>
   <si>
-    <t>Matheus/Vitor/Jackson/Márcio</t>
-  </si>
-  <si>
     <t xml:space="preserve">Av. Dom Hélder Câmara - Alt. R. Cachambi - Sent. Del Castilho - Cachambi </t>
   </si>
   <si>
@@ -9083,9 +9050,6 @@
   </si>
   <si>
     <t xml:space="preserve">Av. Lúcio Costa - Alt. Posto 7 - Sent. Recreio dos Bandeirantes - Barra da Tijuca </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vitor/Carlos/Alex </t>
   </si>
   <si>
     <t>AVENIDA AYRTON SENNA - GARDÊNIA AZUL - ALT. AV. TEN-CEL. MUNIZ DE ARAGÃO</t>
@@ -9197,9 +9161,6 @@
     <t>LINHA VERMELHA - ALT. PONTE DO SABER - SENT. CENTRO</t>
   </si>
   <si>
-    <t>Marcio/ Ricardo/Jackson/Matheus</t>
-  </si>
-  <si>
     <t>AVENIDA RODRIGO OTÁVIO - ALT. Nº1411 - SENT. SÃO CONRADO - GÁVEA</t>
   </si>
   <si>
@@ -9239,9 +9200,6 @@
     <t>Google Maps / Alarme HxGN / Tixxi Cam 3174</t>
   </si>
   <si>
-    <t>Marcio / Vinicius / Diego / Jackson</t>
-  </si>
-  <si>
     <t>VENIDA SALVADOR ALLENDE - ALT. BRT MINHA PRAIA - SENT. TRANSOLIMPICA</t>
   </si>
   <si>
@@ -9320,9 +9278,6 @@
     <t>Maps - TIXXI</t>
   </si>
   <si>
-    <t>Maggessi - Vinícius - Diego</t>
-  </si>
-  <si>
     <t>RUA PINHEIRO MACHADO - ALT. RUA ÁLVARO CHAVES - SENT. BOTAFOGO - LARANJEIRAS</t>
   </si>
   <si>
@@ -9374,9 +9329,6 @@
     <t>TÚNEL ACÚSTICO RAFAEL MASCARENHAS - ENTRE OS TÚNEIS ZUZU ANGEL E ACÚSTICO - SENT. SÃO CONRADO - GÁVEA</t>
   </si>
   <si>
-    <t xml:space="preserve">Alex /  Carlos / Felipe </t>
-  </si>
-  <si>
     <t>LINHA VERMELHA - ALT. KM 13 - SENT. CENTRO - CORDOVIL</t>
   </si>
   <si>
@@ -9446,9 +9398,6 @@
     <t>LINHA AMARELA - ALT. TÚNEL DA COVANCA  - SENT. BARRA DA TIJUCA - JACAREPAGUÁ</t>
   </si>
   <si>
-    <t xml:space="preserve">Daniel / Carlos / Felipe </t>
-  </si>
-  <si>
     <t>AVENIDA DAS AMÉRICAS - ALT. EST. BRT BOSQUE DA BARRA  - SENT. SÃO CONRADO - BARRA DA TIJUCA</t>
   </si>
   <si>
@@ -9497,9 +9446,6 @@
     <t>AVENIDA TRINTA E UM DE MARÇO - ALT. R. FREI CANECA  - SENT. LARANJEIRAS - CATUMBI</t>
   </si>
   <si>
-    <t xml:space="preserve">Matheus/Ricardo/Jackson/Márcio </t>
-  </si>
-  <si>
     <t xml:space="preserve">R. Cândido Benício - Alt. Nº 2973 - Sent. Madureira - Praça Seca </t>
   </si>
   <si>
@@ -9626,9 +9572,6 @@
     <t xml:space="preserve">Autoestrada Fernando Mac Dowell - Alt. R. Emb. Gabriel Landa - Sent. Gávea - São Conrado </t>
   </si>
   <si>
-    <t>Leonardo/Hugo/Alex</t>
-  </si>
-  <si>
     <t>Autoestrada Fernando Mac Dowell - Alt. Túnel Zuzu Angel - Sent. São Conrado - Rocinha</t>
   </si>
   <si>
@@ -9674,9 +9617,6 @@
     <t>Av. Tenente-Coronel Muniz de Aragão - Alt. Estr. do Eng. D'água - Sent. Anil - Gardênia Azul</t>
   </si>
   <si>
-    <t xml:space="preserve">Maggessi / Vinícius / Felipe </t>
-  </si>
-  <si>
     <t>VENIDA SALVADOR ALLENDE - ALT. AV. DAS AMÉRICAS - SENT. ORLA - RECREIO DOS BANDEIRANTES</t>
   </si>
   <si>
@@ -9695,9 +9635,6 @@
     <t>AC CR X VP</t>
   </si>
   <si>
-    <t>Márcio/Vinícius/Jackson/Felipe</t>
-  </si>
-  <si>
     <t>AVENIDA BRASIL - ALT. PASSARELA 06 - SENT. Z. OESTE - MANGUINHOS</t>
   </si>
   <si>
@@ -9710,9 +9647,6 @@
     <t>Google Maps / Alarme HxGN / Tixxi Cam 5279</t>
   </si>
   <si>
-    <t xml:space="preserve">Matheus/Ricardo/Márcio </t>
-  </si>
-  <si>
     <t xml:space="preserve">R. Goiás - Alt. R. Angelina - Piedade </t>
   </si>
   <si>
@@ -9758,9 +9692,6 @@
     <t>Google Maps / Alarme HxGN / Tixxi Cam 260</t>
   </si>
   <si>
-    <t xml:space="preserve">Matheus/Jackson/Maggessi </t>
-  </si>
-  <si>
     <t>Google Maps / Alarme HxGN / Tixxi Cam 5416</t>
   </si>
   <si>
@@ -9788,9 +9719,6 @@
     <t>Google Maps/Tixxi</t>
   </si>
   <si>
-    <t>Maggessi/Matheus/Jackson</t>
-  </si>
-  <si>
     <t xml:space="preserve"> LINHA VERMELHA - ALT. KM 12.5 - SENT. CENTRO - GALEÃO</t>
   </si>
   <si>
@@ -9809,9 +9737,6 @@
     <t xml:space="preserve">Linha Vermelha - Alt. KM 4 - Sent. Centro - Caju </t>
   </si>
   <si>
-    <t>Leonardo / Hugo / Alex</t>
-  </si>
-  <si>
     <t xml:space="preserve">Rua Prof. Arlindo Rodrigues - Alt. R. Rivadávia Corrêa - Sent. Av. Venezuela - Gamboa </t>
   </si>
   <si>
@@ -9851,9 +9776,6 @@
     <t>Estr. Intendente Magalhães - Alt. R. Conde de Linhares - Sent. Sulacap - Campinho</t>
   </si>
   <si>
-    <t xml:space="preserve">Maggessi / Jackson / Felipe </t>
-  </si>
-  <si>
     <t>VIADUTO SANTIAGO DANTAS - SENT. COPACABANA - BOTAFOGO</t>
   </si>
   <si>
@@ -9863,9 +9785,6 @@
     <t>AVENIDA BRASIL - ALT. CENTRO HOSPITALAR DA FIOCRUZ - SENT. Z. OESTE - MARÉ</t>
   </si>
   <si>
-    <t>Leonardo / Hugo / Daniel</t>
-  </si>
-  <si>
     <t>Av. Prof. Manoel de Abreu - Alt. R. Dona Zumira - Sent. Centro - Maracanã</t>
   </si>
   <si>
@@ -9908,9 +9827,6 @@
     <t>Google Maps / Alarme HxGN / Tixxi Cam 399</t>
   </si>
   <si>
-    <t xml:space="preserve">Márcio / Ricardo  / Felipe </t>
-  </si>
-  <si>
     <t>LINHA AMARELA - ALT. ESTRADA ADHEMAR BEBIANO - SENT. BARRA DA TIJUCA - INHAÚMA</t>
   </si>
   <si>
@@ -9959,9 +9875,6 @@
     <t>VENIDA PASTOR MARTIN LUTHER KING JÚNIOR - ALT. R. ÁLVARO DE MIRANDA - SENT. JACARÉ - INHAÚMA</t>
   </si>
   <si>
-    <t xml:space="preserve">Matheus/Jackson/Vinícius/Márcio </t>
-  </si>
-  <si>
     <t xml:space="preserve">Av. Salvador Allende - Alt. Est. BRT Catedral do Recreio - Sent. Curicica - Barra da Tijuca </t>
   </si>
   <si>
@@ -10035,9 +9948,6 @@
   </si>
   <si>
     <t>Av. Salvador Allende - Alt. Est. BRT Asa Branca - Sent. Recreio - Barra Olímpica</t>
-  </si>
-  <si>
-    <t>Maggessi / Vinícius / Felipe</t>
   </si>
   <si>
     <t>End.: PADRE LEONEL FRANCA - GÁVEA - Sent. São Conrado</t>
@@ -10382,7 +10292,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="14" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -10540,7 +10450,6 @@
     <xf numFmtId="0" fontId="29" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10866,7 +10775,7 @@
         <v>2899</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>3340</v>
+        <v>3310</v>
       </c>
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
@@ -11072,7 +10981,7 @@
         <v>2899</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>3340</v>
+        <v>3310</v>
       </c>
       <c r="P8" s="9"/>
       <c r="Q8" s="9"/>
@@ -51668,10 +51577,10 @@
         <v>23</v>
       </c>
       <c r="E1884" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1884" s="34" t="s">
         <v>2900</v>
-      </c>
-      <c r="F1884" s="34" t="s">
-        <v>2901</v>
       </c>
     </row>
     <row r="1885" spans="2:7" ht="15" customHeight="1">
@@ -51685,10 +51594,10 @@
         <v>2241</v>
       </c>
       <c r="E1885" s="34" t="s">
-        <v>2900</v>
+        <v>11</v>
       </c>
       <c r="F1885" s="34" t="s">
-        <v>2902</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1886" spans="2:7" ht="15" customHeight="1">
@@ -51696,16 +51605,16 @@
         <v>46266</v>
       </c>
       <c r="C1886" s="34" t="s">
-        <v>2903</v>
+        <v>2902</v>
       </c>
       <c r="D1886" s="34" t="s">
         <v>2382</v>
       </c>
       <c r="E1886" s="34" t="s">
-        <v>2900</v>
+        <v>11</v>
       </c>
       <c r="F1886" s="34" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
     </row>
     <row r="1887" spans="2:7" ht="15" customHeight="1">
@@ -51719,10 +51628,10 @@
         <v>42</v>
       </c>
       <c r="E1887" s="34" t="s">
-        <v>2900</v>
+        <v>11</v>
       </c>
       <c r="F1887" s="34" t="s">
-        <v>2905</v>
+        <v>2904</v>
       </c>
     </row>
     <row r="1888" spans="2:7" ht="15" customHeight="1">
@@ -51730,16 +51639,16 @@
         <v>46266</v>
       </c>
       <c r="C1888" s="34" t="s">
-        <v>2906</v>
+        <v>2905</v>
       </c>
       <c r="D1888" s="34" t="s">
         <v>910</v>
       </c>
       <c r="E1888" s="34" t="s">
-        <v>2907</v>
+        <v>11</v>
       </c>
       <c r="F1888" s="34" t="s">
-        <v>2908</v>
+        <v>2906</v>
       </c>
     </row>
     <row r="1889" spans="2:7" ht="15" customHeight="1">
@@ -51753,10 +51662,10 @@
         <v>385</v>
       </c>
       <c r="E1889" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1889" s="34" t="s">
         <v>2907</v>
-      </c>
-      <c r="F1889" s="34" t="s">
-        <v>2909</v>
       </c>
     </row>
     <row r="1890" spans="2:7" ht="15" customHeight="1">
@@ -51770,10 +51679,10 @@
         <v>42</v>
       </c>
       <c r="E1890" s="34" t="s">
-        <v>2907</v>
+        <v>11</v>
       </c>
       <c r="F1890" s="34" t="s">
-        <v>2910</v>
+        <v>2908</v>
       </c>
     </row>
     <row r="1891" spans="2:7" ht="15" customHeight="1">
@@ -51781,13 +51690,13 @@
         <v>46266</v>
       </c>
       <c r="C1891" s="34" t="s">
-        <v>2911</v>
+        <v>2909</v>
       </c>
       <c r="D1891" s="34" t="s">
         <v>352</v>
       </c>
       <c r="E1891" s="34" t="s">
-        <v>2907</v>
+        <v>11</v>
       </c>
       <c r="F1891" s="34" t="s">
         <v>2171</v>
@@ -51804,10 +51713,10 @@
         <v>633</v>
       </c>
       <c r="E1892" s="34" t="s">
-        <v>2907</v>
+        <v>11</v>
       </c>
       <c r="F1892" s="34" t="s">
-        <v>2912</v>
+        <v>2910</v>
       </c>
     </row>
     <row r="1893" spans="2:7" ht="15" customHeight="1">
@@ -51815,16 +51724,16 @@
         <v>46266</v>
       </c>
       <c r="C1893" s="34" t="s">
-        <v>2913</v>
+        <v>2911</v>
       </c>
       <c r="D1893" s="34" t="s">
         <v>719</v>
       </c>
       <c r="E1893" s="34" t="s">
-        <v>2907</v>
+        <v>11</v>
       </c>
       <c r="F1893" s="34" t="s">
-        <v>2914</v>
+        <v>2912</v>
       </c>
     </row>
     <row r="1894" spans="2:7" ht="15" customHeight="1">
@@ -51837,8 +51746,8 @@
       <c r="D1894" s="52" t="s">
         <v>224</v>
       </c>
-      <c r="E1894" s="52" t="s">
-        <v>2915</v>
+      <c r="E1894" s="34" t="s">
+        <v>11</v>
       </c>
       <c r="F1894" s="52" t="s">
         <v>1854</v>
@@ -51857,11 +51766,11 @@
       <c r="D1895" s="52" t="s">
         <v>1132</v>
       </c>
-      <c r="E1895" s="52" t="s">
-        <v>2915</v>
+      <c r="E1895" s="34" t="s">
+        <v>11</v>
       </c>
       <c r="F1895" s="52" t="s">
-        <v>2916</v>
+        <v>2913</v>
       </c>
       <c r="G1895" s="52" t="s">
         <v>51</v>
@@ -51872,16 +51781,16 @@
         <v>46267</v>
       </c>
       <c r="C1896" s="52" t="s">
-        <v>2917</v>
+        <v>2914</v>
       </c>
       <c r="D1896" s="52" t="s">
         <v>1423</v>
       </c>
-      <c r="E1896" s="52" t="s">
+      <c r="E1896" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1896" s="52" t="s">
         <v>2915</v>
-      </c>
-      <c r="F1896" s="52" t="s">
-        <v>2918</v>
       </c>
       <c r="G1896" s="52" t="s">
         <v>51</v>
@@ -51897,11 +51806,11 @@
       <c r="D1897" s="52" t="s">
         <v>1687</v>
       </c>
-      <c r="E1897" s="52" t="s">
-        <v>2915</v>
+      <c r="E1897" s="34" t="s">
+        <v>11</v>
       </c>
       <c r="F1897" s="52" t="s">
-        <v>2919</v>
+        <v>2916</v>
       </c>
       <c r="G1897" s="52" t="s">
         <v>30</v>
@@ -51918,7 +51827,7 @@
         <v>42</v>
       </c>
       <c r="E1898" s="52" t="s">
-        <v>2920</v>
+        <v>28</v>
       </c>
       <c r="F1898" s="52" t="s">
         <v>1043</v>
@@ -51932,16 +51841,16 @@
         <v>46267</v>
       </c>
       <c r="C1899" s="52" t="s">
-        <v>2921</v>
+        <v>2917</v>
       </c>
       <c r="D1899" s="52" t="s">
         <v>121</v>
       </c>
       <c r="E1899" s="52" t="s">
-        <v>2920</v>
+        <v>28</v>
       </c>
       <c r="F1899" s="70" t="s">
-        <v>2922</v>
+        <v>2918</v>
       </c>
       <c r="G1899" s="52" t="s">
         <v>51</v>
@@ -51952,16 +51861,16 @@
         <v>46267</v>
       </c>
       <c r="C1900" s="52" t="s">
-        <v>2923</v>
+        <v>2919</v>
       </c>
       <c r="D1900" s="52" t="s">
         <v>394</v>
       </c>
       <c r="E1900" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1900" s="52" t="s">
         <v>2920</v>
-      </c>
-      <c r="F1900" s="52" t="s">
-        <v>2924</v>
       </c>
       <c r="G1900" s="52" t="s">
         <v>51</v>
@@ -51978,10 +51887,10 @@
         <v>44</v>
       </c>
       <c r="E1901" s="52" t="s">
-        <v>2920</v>
+        <v>28</v>
       </c>
       <c r="F1901" s="52" t="s">
-        <v>2925</v>
+        <v>2921</v>
       </c>
       <c r="G1901" s="52" t="s">
         <v>30</v>
@@ -51998,7 +51907,7 @@
         <v>44</v>
       </c>
       <c r="E1902" s="52" t="s">
-        <v>2920</v>
+        <v>28</v>
       </c>
       <c r="F1902" s="52" t="s">
         <v>2145</v>
@@ -52018,7 +51927,7 @@
         <v>10</v>
       </c>
       <c r="E1903" s="52" t="s">
-        <v>2920</v>
+        <v>28</v>
       </c>
       <c r="F1903" s="53" t="s">
         <v>118</v>
@@ -52038,7 +51947,7 @@
         <v>44</v>
       </c>
       <c r="E1904" s="52" t="s">
-        <v>2920</v>
+        <v>28</v>
       </c>
       <c r="F1904" s="53" t="s">
         <v>578</v>
@@ -52052,16 +51961,16 @@
         <v>46267</v>
       </c>
       <c r="C1905" s="52" t="s">
-        <v>2926</v>
+        <v>2922</v>
       </c>
       <c r="D1905" s="52" t="s">
         <v>10</v>
       </c>
       <c r="E1905" s="52" t="s">
-        <v>2920</v>
+        <v>28</v>
       </c>
       <c r="F1905" s="53" t="s">
-        <v>2927</v>
+        <v>2923</v>
       </c>
       <c r="G1905" s="52" t="s">
         <v>70</v>
@@ -52072,16 +51981,16 @@
         <v>46267</v>
       </c>
       <c r="C1906" s="52" t="s">
-        <v>2928</v>
+        <v>2924</v>
       </c>
       <c r="D1906" s="52" t="s">
         <v>462</v>
       </c>
       <c r="E1906" s="52" t="s">
-        <v>2920</v>
+        <v>28</v>
       </c>
       <c r="F1906" s="53" t="s">
-        <v>2929</v>
+        <v>2925</v>
       </c>
       <c r="G1906" s="52" t="s">
         <v>51</v>
@@ -52092,13 +52001,13 @@
         <v>46267</v>
       </c>
       <c r="C1907" s="52" t="s">
-        <v>2930</v>
+        <v>2926</v>
       </c>
       <c r="D1907" s="52" t="s">
         <v>44</v>
       </c>
       <c r="E1907" s="52" t="s">
-        <v>2920</v>
+        <v>28</v>
       </c>
       <c r="F1907" s="52" t="s">
         <v>2294</v>
@@ -52118,10 +52027,10 @@
         <v>19</v>
       </c>
       <c r="E1908" s="52" t="s">
-        <v>2920</v>
+        <v>28</v>
       </c>
       <c r="F1908" s="53" t="s">
-        <v>2931</v>
+        <v>2927</v>
       </c>
       <c r="G1908" s="52" t="s">
         <v>30</v>
@@ -52132,16 +52041,16 @@
         <v>46267</v>
       </c>
       <c r="C1909" s="52" t="s">
-        <v>2932</v>
+        <v>2928</v>
       </c>
       <c r="D1909" s="52" t="s">
         <v>352</v>
       </c>
       <c r="E1909" s="52" t="s">
-        <v>2920</v>
+        <v>28</v>
       </c>
       <c r="F1909" s="53" t="s">
-        <v>2933</v>
+        <v>2929</v>
       </c>
       <c r="G1909" s="52" t="s">
         <v>51</v>
@@ -52158,10 +52067,10 @@
         <v>44</v>
       </c>
       <c r="E1910" s="52" t="s">
-        <v>2920</v>
+        <v>28</v>
       </c>
       <c r="F1910" s="52" t="s">
-        <v>2934</v>
+        <v>2930</v>
       </c>
       <c r="G1910" s="52" t="s">
         <v>30</v>
@@ -52172,16 +52081,16 @@
         <v>46267</v>
       </c>
       <c r="C1911" s="52" t="s">
-        <v>2935</v>
+        <v>2931</v>
       </c>
       <c r="D1911" s="52" t="s">
         <v>44</v>
       </c>
       <c r="E1911" s="52" t="s">
-        <v>2920</v>
+        <v>28</v>
       </c>
       <c r="F1911" s="52" t="s">
-        <v>2936</v>
+        <v>2932</v>
       </c>
       <c r="G1911" s="52" t="s">
         <v>70</v>
@@ -52198,10 +52107,10 @@
         <v>44</v>
       </c>
       <c r="E1912" s="52" t="s">
-        <v>2920</v>
+        <v>28</v>
       </c>
       <c r="F1912" s="52" t="s">
-        <v>2937</v>
+        <v>2933</v>
       </c>
       <c r="G1912" s="52" t="s">
         <v>30</v>
@@ -52212,16 +52121,16 @@
         <v>46267</v>
       </c>
       <c r="C1913" s="52" t="s">
-        <v>2938</v>
+        <v>2934</v>
       </c>
       <c r="D1913" s="52" t="s">
         <v>62</v>
       </c>
       <c r="E1913" s="52" t="s">
-        <v>2920</v>
+        <v>28</v>
       </c>
       <c r="F1913" s="52" t="s">
-        <v>2939</v>
+        <v>2935</v>
       </c>
       <c r="G1913" s="52" t="s">
         <v>70</v>
@@ -52232,16 +52141,16 @@
         <v>46267</v>
       </c>
       <c r="C1914" s="52" t="s">
-        <v>2940</v>
+        <v>2936</v>
       </c>
       <c r="D1914" s="52" t="s">
-        <v>2941</v>
+        <v>2937</v>
       </c>
       <c r="E1914" s="52" t="s">
-        <v>2942</v>
+        <v>11</v>
       </c>
       <c r="F1914" s="53" t="s">
-        <v>2943</v>
+        <v>2938</v>
       </c>
       <c r="G1914" s="52" t="s">
         <v>51</v>
@@ -52258,10 +52167,10 @@
         <v>969</v>
       </c>
       <c r="E1915" s="52" t="s">
-        <v>2944</v>
+        <v>28</v>
       </c>
       <c r="F1915" s="52" t="s">
-        <v>2945</v>
+        <v>2939</v>
       </c>
       <c r="G1915" s="52" t="s">
         <v>30</v>
@@ -52278,7 +52187,7 @@
         <v>103</v>
       </c>
       <c r="E1916" s="52" t="s">
-        <v>2944</v>
+        <v>28</v>
       </c>
       <c r="F1916" s="52" t="s">
         <v>1437</v>
@@ -52292,16 +52201,16 @@
         <v>46268</v>
       </c>
       <c r="C1917" s="52" t="s">
-        <v>2946</v>
+        <v>2940</v>
       </c>
       <c r="D1917" s="52" t="s">
         <v>462</v>
       </c>
       <c r="E1917" s="52" t="s">
-        <v>2944</v>
+        <v>28</v>
       </c>
       <c r="F1917" s="52" t="s">
-        <v>2947</v>
+        <v>2941</v>
       </c>
       <c r="G1917" s="52" t="s">
         <v>187</v>
@@ -52312,19 +52221,19 @@
         <v>46268</v>
       </c>
       <c r="C1918" s="52" t="s">
-        <v>2948</v>
+        <v>2942</v>
       </c>
       <c r="D1918" s="52" t="s">
         <v>462</v>
       </c>
       <c r="E1918" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1918" s="52" t="s">
+        <v>2943</v>
+      </c>
+      <c r="G1918" s="52" t="s">
         <v>2944</v>
-      </c>
-      <c r="F1918" s="52" t="s">
-        <v>2949</v>
-      </c>
-      <c r="G1918" s="52" t="s">
-        <v>2950</v>
       </c>
     </row>
     <row r="1919" spans="2:7" ht="15" customHeight="1">
@@ -52338,10 +52247,10 @@
         <v>44</v>
       </c>
       <c r="E1919" s="52" t="s">
-        <v>2944</v>
+        <v>28</v>
       </c>
       <c r="F1919" s="52" t="s">
-        <v>2951</v>
+        <v>2945</v>
       </c>
       <c r="G1919" s="52" t="s">
         <v>30</v>
@@ -52358,13 +52267,13 @@
         <v>2515</v>
       </c>
       <c r="E1920" s="52" t="s">
-        <v>2944</v>
+        <v>28</v>
       </c>
       <c r="F1920" s="52" t="s">
-        <v>2952</v>
+        <v>2946</v>
       </c>
       <c r="G1920" s="52" t="s">
-        <v>2953</v>
+        <v>2947</v>
       </c>
     </row>
     <row r="1921" spans="2:7" ht="15" customHeight="1">
@@ -52378,7 +52287,7 @@
         <v>456</v>
       </c>
       <c r="E1921" s="52" t="s">
-        <v>2944</v>
+        <v>28</v>
       </c>
       <c r="F1921" s="52" t="s">
         <v>578</v>
@@ -52392,16 +52301,16 @@
         <v>46268</v>
       </c>
       <c r="C1922" s="52" t="s">
-        <v>2954</v>
+        <v>2948</v>
       </c>
       <c r="D1922" s="52" t="s">
         <v>52</v>
       </c>
       <c r="E1922" s="52" t="s">
-        <v>2944</v>
+        <v>28</v>
       </c>
       <c r="F1922" s="52" t="s">
-        <v>2955</v>
+        <v>2949</v>
       </c>
       <c r="G1922" s="52" t="s">
         <v>83</v>
@@ -52412,16 +52321,16 @@
         <v>46268</v>
       </c>
       <c r="C1923" s="52" t="s">
-        <v>2954</v>
+        <v>2948</v>
       </c>
       <c r="D1923" s="52" t="s">
         <v>52</v>
       </c>
       <c r="E1923" s="52" t="s">
-        <v>2944</v>
+        <v>28</v>
       </c>
       <c r="F1923" s="52" t="s">
-        <v>2955</v>
+        <v>2949</v>
       </c>
       <c r="G1923" s="52" t="s">
         <v>83</v>
@@ -52432,16 +52341,16 @@
         <v>46268</v>
       </c>
       <c r="C1924" s="52" t="s">
-        <v>2956</v>
+        <v>2950</v>
       </c>
       <c r="D1924" s="52" t="s">
         <v>44</v>
       </c>
       <c r="E1924" s="52" t="s">
-        <v>2944</v>
+        <v>28</v>
       </c>
       <c r="F1924" s="53" t="s">
-        <v>2957</v>
+        <v>2951</v>
       </c>
       <c r="G1924" s="52" t="s">
         <v>83</v>
@@ -52452,16 +52361,16 @@
         <v>46268</v>
       </c>
       <c r="C1925" s="52" t="s">
-        <v>2958</v>
+        <v>2952</v>
       </c>
       <c r="D1925" s="52" t="s">
         <v>937</v>
       </c>
       <c r="E1925" s="52" t="s">
-        <v>2944</v>
+        <v>28</v>
       </c>
       <c r="F1925" s="53" t="s">
-        <v>2959</v>
+        <v>2953</v>
       </c>
       <c r="G1925" s="52" t="s">
         <v>30</v>
@@ -52478,10 +52387,10 @@
         <v>19</v>
       </c>
       <c r="E1926" s="52" t="s">
-        <v>2944</v>
+        <v>28</v>
       </c>
       <c r="F1926" s="53" t="s">
-        <v>2960</v>
+        <v>2954</v>
       </c>
       <c r="G1926" s="52" t="s">
         <v>30</v>
@@ -52498,10 +52407,10 @@
         <v>52</v>
       </c>
       <c r="E1927" s="52" t="s">
-        <v>2944</v>
+        <v>28</v>
       </c>
       <c r="F1927" s="53" t="s">
-        <v>2961</v>
+        <v>2955</v>
       </c>
       <c r="G1927" s="52" t="s">
         <v>30</v>
@@ -52518,7 +52427,7 @@
         <v>15</v>
       </c>
       <c r="E1928" s="52" t="s">
-        <v>2944</v>
+        <v>28</v>
       </c>
       <c r="F1928" s="52" t="s">
         <v>2192</v>
@@ -52538,10 +52447,10 @@
         <v>52</v>
       </c>
       <c r="E1929" s="52" t="s">
-        <v>2944</v>
+        <v>28</v>
       </c>
       <c r="F1929" s="53" t="s">
-        <v>2962</v>
+        <v>2956</v>
       </c>
       <c r="G1929" s="52" t="s">
         <v>2027</v>
@@ -52558,10 +52467,10 @@
         <v>52</v>
       </c>
       <c r="E1930" s="52" t="s">
-        <v>2944</v>
+        <v>28</v>
       </c>
       <c r="F1930" s="53" t="s">
-        <v>2962</v>
+        <v>2956</v>
       </c>
       <c r="G1930" s="52" t="s">
         <v>2027</v>
@@ -52572,16 +52481,16 @@
         <v>46268</v>
       </c>
       <c r="C1931" s="52" t="s">
-        <v>2963</v>
+        <v>2957</v>
       </c>
       <c r="D1931" s="52" t="s">
         <v>19</v>
       </c>
       <c r="E1931" s="52" t="s">
-        <v>2944</v>
+        <v>28</v>
       </c>
       <c r="F1931" s="52" t="s">
-        <v>2964</v>
+        <v>2958</v>
       </c>
       <c r="G1931" s="52" t="s">
         <v>83</v>
@@ -52598,7 +52507,7 @@
         <v>52</v>
       </c>
       <c r="E1932" s="52" t="s">
-        <v>2944</v>
+        <v>28</v>
       </c>
       <c r="F1932" s="52" t="s">
         <v>593</v>
@@ -52618,7 +52527,7 @@
         <v>213</v>
       </c>
       <c r="E1933" s="52" t="s">
-        <v>2944</v>
+        <v>28</v>
       </c>
       <c r="F1933" s="52" t="s">
         <v>578</v>
@@ -52638,10 +52547,10 @@
         <v>62</v>
       </c>
       <c r="E1934" s="52" t="s">
-        <v>2944</v>
+        <v>28</v>
       </c>
       <c r="F1934" s="52" t="s">
-        <v>2965</v>
+        <v>2959</v>
       </c>
       <c r="G1934" s="52" t="s">
         <v>2027</v>
@@ -52652,19 +52561,19 @@
         <v>46268</v>
       </c>
       <c r="C1935" s="52" t="s">
-        <v>2966</v>
+        <v>2960</v>
       </c>
       <c r="D1935" s="52" t="s">
-        <v>2967</v>
+        <v>2961</v>
       </c>
       <c r="E1935" s="52" t="s">
-        <v>2944</v>
+        <v>28</v>
       </c>
       <c r="F1935" s="53" t="s">
-        <v>2968</v>
+        <v>2962</v>
       </c>
       <c r="G1935" s="52" t="s">
-        <v>2967</v>
+        <v>2961</v>
       </c>
     </row>
     <row r="1936" spans="2:7" ht="15" customHeight="1">
@@ -52672,16 +52581,16 @@
         <v>46268</v>
       </c>
       <c r="C1936" s="34" t="s">
-        <v>2969</v>
+        <v>2963</v>
       </c>
       <c r="D1936" s="34" t="s">
         <v>681</v>
       </c>
       <c r="E1936" s="34" t="s">
-        <v>2970</v>
+        <v>11</v>
       </c>
       <c r="F1936" s="34" t="s">
-        <v>2971</v>
+        <v>2964</v>
       </c>
       <c r="G1936" s="34" t="s">
         <v>34</v>
@@ -52692,16 +52601,16 @@
         <v>46268</v>
       </c>
       <c r="C1937" s="34" t="s">
-        <v>2972</v>
+        <v>2965</v>
       </c>
       <c r="D1937" s="34" t="s">
         <v>19</v>
       </c>
       <c r="E1937" s="34" t="s">
-        <v>2970</v>
+        <v>11</v>
       </c>
       <c r="F1937" s="34" t="s">
-        <v>2973</v>
+        <v>2966</v>
       </c>
       <c r="G1937" s="34" t="s">
         <v>34</v>
@@ -52712,16 +52621,16 @@
         <v>46268</v>
       </c>
       <c r="C1938" s="34" t="s">
-        <v>2966</v>
+        <v>2960</v>
       </c>
       <c r="D1938" s="34" t="s">
         <v>1523</v>
       </c>
       <c r="E1938" s="34" t="s">
-        <v>2970</v>
+        <v>11</v>
       </c>
       <c r="F1938" s="34" t="s">
-        <v>2974</v>
+        <v>2967</v>
       </c>
       <c r="G1938" s="34" t="s">
         <v>34</v>
@@ -52732,16 +52641,16 @@
         <v>46272</v>
       </c>
       <c r="C1939" s="34" t="s">
-        <v>2975</v>
+        <v>2968</v>
       </c>
       <c r="D1939" s="34" t="s">
         <v>1406</v>
       </c>
       <c r="E1939" s="34" t="s">
-        <v>2942</v>
+        <v>11</v>
       </c>
       <c r="F1939" s="34" t="s">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="G1939" s="34" t="s">
         <v>34</v>
@@ -52753,16 +52662,16 @@
         <v>46272</v>
       </c>
       <c r="C1940" s="34" t="s">
-        <v>2977</v>
+        <v>2970</v>
       </c>
       <c r="D1940" s="34" t="s">
         <v>42</v>
       </c>
       <c r="E1940" s="34" t="s">
-        <v>2942</v>
+        <v>11</v>
       </c>
       <c r="F1940" s="34" t="s">
-        <v>2978</v>
+        <v>2971</v>
       </c>
       <c r="G1940" s="34" t="s">
         <v>34</v>
@@ -52779,11 +52688,11 @@
       <c r="D1941" s="52" t="s">
         <v>207</v>
       </c>
-      <c r="E1941" s="52" t="s">
-        <v>2979</v>
+      <c r="E1941" s="34" t="s">
+        <v>11</v>
       </c>
       <c r="F1941" s="52" t="s">
-        <v>2980</v>
+        <v>2972</v>
       </c>
       <c r="G1941" s="52" t="s">
         <v>34</v>
@@ -52795,16 +52704,16 @@
         <v>46272</v>
       </c>
       <c r="C1942" s="34" t="s">
-        <v>2981</v>
+        <v>2973</v>
       </c>
       <c r="D1942" s="34" t="s">
-        <v>2982</v>
+        <v>2974</v>
       </c>
       <c r="E1942" s="34" t="s">
-        <v>2970</v>
+        <v>11</v>
       </c>
       <c r="F1942" s="34" t="s">
-        <v>2983</v>
+        <v>2975</v>
       </c>
       <c r="G1942" s="34" t="s">
         <v>34</v>
@@ -52816,16 +52725,16 @@
         <v>46272</v>
       </c>
       <c r="C1943" s="34" t="s">
-        <v>2984</v>
+        <v>2976</v>
       </c>
       <c r="D1943" s="34" t="s">
         <v>207</v>
       </c>
       <c r="E1943" s="34" t="s">
-        <v>2970</v>
+        <v>11</v>
       </c>
       <c r="F1943" s="34" t="s">
-        <v>2985</v>
+        <v>2977</v>
       </c>
       <c r="G1943" s="34" t="s">
         <v>34</v>
@@ -52837,16 +52746,16 @@
         <v>46272</v>
       </c>
       <c r="C1944" s="34" t="s">
-        <v>2972</v>
+        <v>2965</v>
       </c>
       <c r="D1944" s="34" t="s">
         <v>81</v>
       </c>
       <c r="E1944" s="34" t="s">
-        <v>2970</v>
+        <v>11</v>
       </c>
       <c r="F1944" s="34" t="s">
-        <v>2986</v>
+        <v>2978</v>
       </c>
       <c r="G1944" s="34" t="s">
         <v>34</v>
@@ -52858,16 +52767,16 @@
         <v>46272</v>
       </c>
       <c r="C1945" s="34" t="s">
-        <v>2987</v>
+        <v>2979</v>
       </c>
       <c r="D1945" s="34" t="s">
         <v>23</v>
       </c>
       <c r="E1945" s="34" t="s">
-        <v>2970</v>
+        <v>11</v>
       </c>
       <c r="F1945" s="34" t="s">
-        <v>2988</v>
+        <v>2980</v>
       </c>
       <c r="G1945" s="34" t="s">
         <v>41</v>
@@ -52878,16 +52787,16 @@
         <v>46273</v>
       </c>
       <c r="C1946" s="52" t="s">
-        <v>2989</v>
+        <v>2981</v>
       </c>
       <c r="D1946" s="52" t="s">
         <v>23</v>
       </c>
       <c r="E1946" s="52" t="s">
-        <v>2990</v>
+        <v>28</v>
       </c>
       <c r="F1946" s="52" t="s">
-        <v>2991</v>
+        <v>2982</v>
       </c>
       <c r="G1946" s="52" t="s">
         <v>83</v>
@@ -52904,8 +52813,8 @@
       <c r="D1947" s="52" t="s">
         <v>44</v>
       </c>
-      <c r="E1947" s="52" t="s">
-        <v>2992</v>
+      <c r="E1947" s="34" t="s">
+        <v>11</v>
       </c>
       <c r="F1947" s="52" t="s">
         <v>2717</v>
@@ -52920,16 +52829,16 @@
         <v>46273</v>
       </c>
       <c r="C1948" s="52" t="s">
-        <v>2993</v>
+        <v>2983</v>
       </c>
       <c r="D1948" s="52" t="s">
         <v>81</v>
       </c>
-      <c r="E1948" s="52" t="s">
-        <v>2992</v>
+      <c r="E1948" s="34" t="s">
+        <v>11</v>
       </c>
       <c r="F1948" s="52" t="s">
-        <v>2994</v>
+        <v>2984</v>
       </c>
       <c r="G1948" s="52" t="s">
         <v>34</v>
@@ -52941,16 +52850,16 @@
         <v>46273</v>
       </c>
       <c r="C1949" s="52" t="s">
-        <v>2995</v>
+        <v>2985</v>
       </c>
       <c r="D1949" s="52" t="s">
         <v>385</v>
       </c>
-      <c r="E1949" s="52" t="s">
-        <v>2992</v>
+      <c r="E1949" s="34" t="s">
+        <v>11</v>
       </c>
       <c r="F1949" s="52" t="s">
-        <v>2996</v>
+        <v>2986</v>
       </c>
       <c r="G1949" s="52" t="s">
         <v>51</v>
@@ -52967,11 +52876,11 @@
       <c r="D1950" s="52" t="s">
         <v>385</v>
       </c>
-      <c r="E1950" s="52" t="s">
-        <v>2992</v>
+      <c r="E1950" s="34" t="s">
+        <v>11</v>
       </c>
       <c r="F1950" s="52" t="s">
-        <v>2997</v>
+        <v>2987</v>
       </c>
       <c r="G1950" s="52" t="s">
         <v>64</v>
@@ -52988,11 +52897,11 @@
       <c r="D1951" s="52" t="s">
         <v>385</v>
       </c>
-      <c r="E1951" s="52" t="s">
-        <v>2992</v>
+      <c r="E1951" s="34" t="s">
+        <v>11</v>
       </c>
       <c r="F1951" s="52" t="s">
-        <v>2998</v>
+        <v>2988</v>
       </c>
       <c r="G1951" s="52" t="s">
         <v>64</v>
@@ -53009,11 +52918,11 @@
       <c r="D1952" s="52" t="s">
         <v>385</v>
       </c>
-      <c r="E1952" s="52" t="s">
-        <v>2992</v>
+      <c r="E1952" s="34" t="s">
+        <v>11</v>
       </c>
       <c r="F1952" s="52" t="s">
-        <v>2999</v>
+        <v>2989</v>
       </c>
       <c r="G1952" s="52" t="s">
         <v>64</v>
@@ -53025,16 +52934,16 @@
         <v>46273</v>
       </c>
       <c r="C1953" s="52" t="s">
-        <v>3000</v>
+        <v>2990</v>
       </c>
       <c r="D1953" s="52" t="s">
         <v>1991</v>
       </c>
-      <c r="E1953" s="52" t="s">
-        <v>2992</v>
+      <c r="E1953" s="34" t="s">
+        <v>11</v>
       </c>
       <c r="F1953" s="52" t="s">
-        <v>3001</v>
+        <v>2991</v>
       </c>
       <c r="G1953" s="52" t="s">
         <v>51</v>
@@ -53046,16 +52955,16 @@
         <v>46273</v>
       </c>
       <c r="C1954" s="52" t="s">
-        <v>3002</v>
+        <v>2992</v>
       </c>
       <c r="D1954" s="52" t="s">
         <v>1991</v>
       </c>
-      <c r="E1954" s="52" t="s">
-        <v>2992</v>
+      <c r="E1954" s="34" t="s">
+        <v>11</v>
       </c>
       <c r="F1954" s="52" t="s">
-        <v>3003</v>
+        <v>2993</v>
       </c>
       <c r="G1954" s="52" t="s">
         <v>51</v>
@@ -53066,16 +52975,16 @@
         <v>46274</v>
       </c>
       <c r="C1955" s="54" t="s">
-        <v>3004</v>
+        <v>2994</v>
       </c>
       <c r="D1955" s="54" t="s">
         <v>570</v>
       </c>
-      <c r="E1955" s="54" t="s">
-        <v>2992</v>
+      <c r="E1955" s="34" t="s">
+        <v>11</v>
       </c>
       <c r="F1955" s="54" t="s">
-        <v>3005</v>
+        <v>2995</v>
       </c>
       <c r="G1955" s="54" t="s">
         <v>51</v>
@@ -53092,11 +53001,11 @@
       <c r="D1956" s="54" t="s">
         <v>385</v>
       </c>
-      <c r="E1956" s="54" t="s">
-        <v>2992</v>
+      <c r="E1956" s="34" t="s">
+        <v>11</v>
       </c>
       <c r="F1956" s="54" t="s">
-        <v>3006</v>
+        <v>2996</v>
       </c>
       <c r="G1956" s="54" t="s">
         <v>41</v>
@@ -53108,16 +53017,16 @@
         <v>46274</v>
       </c>
       <c r="C1957" s="54" t="s">
-        <v>3007</v>
+        <v>2997</v>
       </c>
       <c r="D1957" s="54" t="s">
         <v>385</v>
       </c>
-      <c r="E1957" s="54" t="s">
-        <v>3008</v>
+      <c r="E1957" s="34" t="s">
+        <v>11</v>
       </c>
       <c r="F1957" s="54" t="s">
-        <v>3009</v>
+        <v>2998</v>
       </c>
       <c r="G1957" s="54" t="s">
         <v>51</v>
@@ -53129,16 +53038,16 @@
         <v>46274</v>
       </c>
       <c r="C1958" s="54" t="s">
-        <v>3010</v>
+        <v>2999</v>
       </c>
       <c r="D1958" s="54" t="s">
-        <v>3011</v>
-      </c>
-      <c r="E1958" s="54" t="s">
-        <v>3008</v>
+        <v>3000</v>
+      </c>
+      <c r="E1958" s="34" t="s">
+        <v>11</v>
       </c>
       <c r="F1958" s="54" t="s">
-        <v>3012</v>
+        <v>3001</v>
       </c>
       <c r="G1958" s="54" t="s">
         <v>51</v>
@@ -53155,11 +53064,11 @@
       <c r="D1959" s="54" t="s">
         <v>23</v>
       </c>
-      <c r="E1959" s="54" t="s">
-        <v>3008</v>
+      <c r="E1959" s="34" t="s">
+        <v>11</v>
       </c>
       <c r="F1959" s="54" t="s">
-        <v>3013</v>
+        <v>3002</v>
       </c>
       <c r="G1959" s="54" t="s">
         <v>64</v>
@@ -53177,10 +53086,10 @@
         <v>462</v>
       </c>
       <c r="E1960" s="54" t="s">
-        <v>3014</v>
+        <v>28</v>
       </c>
       <c r="F1960" s="54" t="s">
-        <v>3015</v>
+        <v>3003</v>
       </c>
       <c r="G1960" s="54" t="s">
         <v>191</v>
@@ -53198,10 +53107,10 @@
         <v>570</v>
       </c>
       <c r="E1961" s="54" t="s">
-        <v>3014</v>
+        <v>28</v>
       </c>
       <c r="F1961" s="54" t="s">
-        <v>3016</v>
+        <v>3004</v>
       </c>
       <c r="G1961" s="54" t="s">
         <v>191</v>
@@ -53219,10 +53128,10 @@
         <v>403</v>
       </c>
       <c r="E1962" s="54" t="s">
-        <v>3014</v>
+        <v>28</v>
       </c>
       <c r="F1962" s="54" t="s">
-        <v>3017</v>
+        <v>3005</v>
       </c>
       <c r="G1962" s="54" t="s">
         <v>191</v>
@@ -53240,10 +53149,10 @@
         <v>462</v>
       </c>
       <c r="E1963" s="54" t="s">
-        <v>3014</v>
+        <v>28</v>
       </c>
       <c r="F1963" s="54" t="s">
-        <v>3018</v>
+        <v>3006</v>
       </c>
       <c r="G1963" s="54" t="s">
         <v>191</v>
@@ -53261,10 +53170,10 @@
         <v>462</v>
       </c>
       <c r="E1964" s="54" t="s">
-        <v>3014</v>
+        <v>28</v>
       </c>
       <c r="F1964" s="54" t="s">
-        <v>3019</v>
+        <v>3007</v>
       </c>
       <c r="G1964" s="54" t="s">
         <v>191</v>
@@ -53282,10 +53191,10 @@
         <v>213</v>
       </c>
       <c r="E1965" s="54" t="s">
-        <v>3014</v>
+        <v>28</v>
       </c>
       <c r="F1965" s="54" t="s">
-        <v>3020</v>
+        <v>3008</v>
       </c>
       <c r="G1965" s="54" t="s">
         <v>191</v>
@@ -53303,10 +53212,10 @@
         <v>23</v>
       </c>
       <c r="E1966" s="54" t="s">
-        <v>3014</v>
+        <v>28</v>
       </c>
       <c r="F1966" s="54" t="s">
-        <v>3021</v>
+        <v>3009</v>
       </c>
       <c r="G1966" s="54" t="s">
         <v>34</v>
@@ -53318,16 +53227,16 @@
         <v>46274</v>
       </c>
       <c r="C1967" s="54" t="s">
-        <v>3022</v>
+        <v>3010</v>
       </c>
       <c r="D1967" s="54" t="s">
-        <v>3023</v>
-      </c>
-      <c r="E1967" s="54" t="s">
-        <v>2907</v>
+        <v>3011</v>
+      </c>
+      <c r="E1967" s="34" t="s">
+        <v>11</v>
       </c>
       <c r="F1967" s="54" t="s">
-        <v>3024</v>
+        <v>3012</v>
       </c>
       <c r="G1967" s="54" t="s">
         <v>51</v>
@@ -53339,16 +53248,16 @@
         <v>46274</v>
       </c>
       <c r="C1968" s="54" t="s">
-        <v>3025</v>
+        <v>3013</v>
       </c>
       <c r="D1968" s="54" t="s">
         <v>403</v>
       </c>
-      <c r="E1968" s="54" t="s">
-        <v>2907</v>
+      <c r="E1968" s="34" t="s">
+        <v>11</v>
       </c>
       <c r="F1968" s="54" t="s">
-        <v>3026</v>
+        <v>3014</v>
       </c>
       <c r="G1968" s="54" t="s">
         <v>51</v>
@@ -53360,16 +53269,16 @@
         <v>46274</v>
       </c>
       <c r="C1969" s="55" t="s">
-        <v>3027</v>
+        <v>3015</v>
       </c>
       <c r="D1969" s="54" t="s">
         <v>385</v>
       </c>
-      <c r="E1969" s="54" t="s">
-        <v>2907</v>
+      <c r="E1969" s="34" t="s">
+        <v>11</v>
       </c>
       <c r="F1969" s="54" t="s">
-        <v>3028</v>
+        <v>3016</v>
       </c>
       <c r="G1969" s="54" t="s">
         <v>51</v>
@@ -53381,16 +53290,16 @@
         <v>46274</v>
       </c>
       <c r="C1970" s="55" t="s">
-        <v>3029</v>
+        <v>3017</v>
       </c>
       <c r="D1970" s="54" t="s">
         <v>385</v>
       </c>
-      <c r="E1970" s="54" t="s">
-        <v>2907</v>
+      <c r="E1970" s="34" t="s">
+        <v>11</v>
       </c>
       <c r="F1970" s="54" t="s">
-        <v>3030</v>
+        <v>3018</v>
       </c>
       <c r="G1970" s="54" t="s">
         <v>51</v>
@@ -53402,16 +53311,16 @@
         <v>46274</v>
       </c>
       <c r="C1971" s="55" t="s">
-        <v>2993</v>
+        <v>2983</v>
       </c>
       <c r="D1971" s="54" t="s">
         <v>1860</v>
       </c>
-      <c r="E1971" s="54" t="s">
-        <v>2907</v>
+      <c r="E1971" s="34" t="s">
+        <v>11</v>
       </c>
       <c r="F1971" s="54" t="s">
-        <v>3031</v>
+        <v>3019</v>
       </c>
       <c r="G1971" s="54" t="s">
         <v>51</v>
@@ -53423,16 +53332,16 @@
         <v>46274</v>
       </c>
       <c r="C1972" s="55" t="s">
-        <v>3032</v>
+        <v>3020</v>
       </c>
       <c r="D1972" s="54" t="s">
         <v>42</v>
       </c>
-      <c r="E1972" s="54" t="s">
-        <v>2907</v>
+      <c r="E1972" s="34" t="s">
+        <v>11</v>
       </c>
       <c r="F1972" s="54" t="s">
-        <v>3033</v>
+        <v>3021</v>
       </c>
       <c r="G1972" s="54" t="s">
         <v>51</v>
@@ -53443,16 +53352,16 @@
         <v>46275</v>
       </c>
       <c r="C1973" s="71" t="s">
-        <v>3034</v>
+        <v>3022</v>
       </c>
       <c r="D1973" s="52" t="s">
         <v>570</v>
       </c>
-      <c r="E1973" s="52" t="s">
-        <v>2907</v>
+      <c r="E1973" s="34" t="s">
+        <v>11</v>
       </c>
       <c r="F1973" s="52" t="s">
-        <v>3035</v>
+        <v>3023</v>
       </c>
       <c r="G1973" s="52" t="s">
         <v>51</v>
@@ -53469,11 +53378,11 @@
       <c r="D1974" s="52" t="s">
         <v>207</v>
       </c>
-      <c r="E1974" s="52" t="s">
-        <v>2907</v>
+      <c r="E1974" s="34" t="s">
+        <v>11</v>
       </c>
       <c r="F1974" s="72" t="s">
-        <v>3036</v>
+        <v>3024</v>
       </c>
       <c r="G1974" s="52" t="s">
         <v>30</v>
@@ -53485,16 +53394,16 @@
         <v>46275</v>
       </c>
       <c r="C1975" s="52" t="s">
-        <v>2930</v>
+        <v>2926</v>
       </c>
       <c r="D1975" s="52" t="s">
         <v>612</v>
       </c>
-      <c r="E1975" s="52" t="s">
-        <v>2907</v>
+      <c r="E1975" s="34" t="s">
+        <v>11</v>
       </c>
       <c r="F1975" s="52" t="s">
-        <v>3006</v>
+        <v>2996</v>
       </c>
       <c r="G1975" s="52" t="s">
         <v>51</v>
@@ -53506,16 +53415,16 @@
         <v>46275</v>
       </c>
       <c r="C1976" s="52" t="s">
-        <v>3037</v>
+        <v>3025</v>
       </c>
       <c r="D1976" s="52" t="s">
         <v>38</v>
       </c>
-      <c r="E1976" s="52" t="s">
-        <v>2944</v>
+      <c r="E1976" s="54" t="s">
+        <v>28</v>
       </c>
       <c r="F1976" s="52" t="s">
-        <v>2951</v>
+        <v>2945</v>
       </c>
       <c r="G1976" s="52" t="s">
         <v>51</v>
@@ -53532,8 +53441,8 @@
       <c r="D1977" s="52" t="s">
         <v>15</v>
       </c>
-      <c r="E1977" s="52" t="s">
-        <v>2944</v>
+      <c r="E1977" s="54" t="s">
+        <v>28</v>
       </c>
       <c r="F1977" s="52" t="s">
         <v>578</v>
@@ -53553,8 +53462,8 @@
       <c r="D1978" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="E1978" s="52" t="s">
-        <v>2944</v>
+      <c r="E1978" s="54" t="s">
+        <v>28</v>
       </c>
       <c r="F1978" s="52" t="s">
         <v>2039</v>
@@ -53574,8 +53483,8 @@
       <c r="D1979" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="E1979" s="52" t="s">
-        <v>2944</v>
+      <c r="E1979" s="54" t="s">
+        <v>28</v>
       </c>
       <c r="F1979" s="52" t="s">
         <v>578</v>
@@ -53595,11 +53504,11 @@
       <c r="D1980" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="E1980" s="52" t="s">
-        <v>2944</v>
+      <c r="E1980" s="54" t="s">
+        <v>28</v>
       </c>
       <c r="F1980" s="52" t="s">
-        <v>3038</v>
+        <v>3026</v>
       </c>
       <c r="G1980" s="52" t="s">
         <v>30</v>
@@ -53611,13 +53520,13 @@
         <v>46275</v>
       </c>
       <c r="C1981" s="52" t="s">
-        <v>3039</v>
+        <v>3027</v>
       </c>
       <c r="D1981" s="52" t="s">
         <v>570</v>
       </c>
-      <c r="E1981" s="52" t="s">
-        <v>2944</v>
+      <c r="E1981" s="54" t="s">
+        <v>28</v>
       </c>
       <c r="F1981" s="52" t="s">
         <v>1506</v>
@@ -53632,16 +53541,16 @@
         <v>46275</v>
       </c>
       <c r="C1982" s="52" t="s">
-        <v>3040</v>
+        <v>3028</v>
       </c>
       <c r="D1982" s="52" t="s">
         <v>213</v>
       </c>
-      <c r="E1982" s="52" t="s">
-        <v>2944</v>
+      <c r="E1982" s="54" t="s">
+        <v>28</v>
       </c>
       <c r="F1982" s="52" t="s">
-        <v>3041</v>
+        <v>3029</v>
       </c>
       <c r="G1982" s="52" t="s">
         <v>30</v>
@@ -53658,8 +53567,8 @@
       <c r="D1983" s="52" t="s">
         <v>44</v>
       </c>
-      <c r="E1983" s="52" t="s">
-        <v>2944</v>
+      <c r="E1983" s="54" t="s">
+        <v>28</v>
       </c>
       <c r="F1983" s="52" t="s">
         <v>1571</v>
@@ -53674,16 +53583,16 @@
         <v>46275</v>
       </c>
       <c r="C1984" s="52" t="s">
-        <v>3042</v>
+        <v>3030</v>
       </c>
       <c r="D1984" s="52" t="s">
         <v>352</v>
       </c>
-      <c r="E1984" s="52" t="s">
-        <v>2944</v>
+      <c r="E1984" s="54" t="s">
+        <v>28</v>
       </c>
       <c r="F1984" s="52" t="s">
-        <v>3043</v>
+        <v>3031</v>
       </c>
       <c r="G1984" s="52" t="s">
         <v>30</v>
@@ -53695,16 +53604,16 @@
         <v>46275</v>
       </c>
       <c r="C1985" s="52" t="s">
-        <v>3004</v>
+        <v>2994</v>
       </c>
       <c r="D1985" s="52" t="s">
         <v>213</v>
       </c>
-      <c r="E1985" s="52" t="s">
-        <v>2944</v>
+      <c r="E1985" s="54" t="s">
+        <v>28</v>
       </c>
       <c r="F1985" s="52" t="s">
-        <v>3044</v>
+        <v>3032</v>
       </c>
       <c r="G1985" s="52" t="s">
         <v>51</v>
@@ -53721,11 +53630,11 @@
       <c r="D1986" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="E1986" s="52" t="s">
-        <v>2944</v>
+      <c r="E1986" s="54" t="s">
+        <v>28</v>
       </c>
       <c r="F1986" s="52" t="s">
-        <v>3045</v>
+        <v>3033</v>
       </c>
       <c r="G1986" s="52" t="s">
         <v>371</v>
@@ -53737,16 +53646,16 @@
         <v>46275</v>
       </c>
       <c r="C1987" s="52" t="s">
-        <v>3046</v>
+        <v>3034</v>
       </c>
       <c r="D1987" s="52" t="s">
         <v>2583</v>
       </c>
       <c r="E1987" s="52" t="s">
-        <v>2942</v>
+        <v>11</v>
       </c>
       <c r="F1987" s="52" t="s">
-        <v>3047</v>
+        <v>3035</v>
       </c>
       <c r="G1987" s="52" t="s">
         <v>51</v>
@@ -53757,16 +53666,16 @@
         <v>46276</v>
       </c>
       <c r="C1988" s="52" t="s">
-        <v>3048</v>
+        <v>3036</v>
       </c>
       <c r="D1988" s="52" t="s">
-        <v>3049</v>
+        <v>3037</v>
       </c>
       <c r="E1988" s="52" t="s">
-        <v>2942</v>
+        <v>11</v>
       </c>
       <c r="F1988" s="52" t="s">
-        <v>3050</v>
+        <v>3038</v>
       </c>
       <c r="G1988" s="52" t="s">
         <v>34</v>
@@ -53783,10 +53692,10 @@
         <v>207</v>
       </c>
       <c r="E1989" s="52" t="s">
-        <v>3051</v>
+        <v>11</v>
       </c>
       <c r="F1989" s="52" t="s">
-        <v>3052</v>
+        <v>3039</v>
       </c>
       <c r="G1989" s="52" t="s">
         <v>70</v>
@@ -53801,13 +53710,13 @@
         <v>2167</v>
       </c>
       <c r="D1990" s="52" t="s">
-        <v>3053</v>
+        <v>3040</v>
       </c>
       <c r="E1990" s="52" t="s">
-        <v>3051</v>
+        <v>11</v>
       </c>
       <c r="F1990" s="52" t="s">
-        <v>3054</v>
+        <v>3041</v>
       </c>
       <c r="G1990" s="52" t="s">
         <v>34</v>
@@ -53825,7 +53734,7 @@
         <v>207</v>
       </c>
       <c r="E1991" s="52" t="s">
-        <v>3051</v>
+        <v>11</v>
       </c>
       <c r="F1991" s="52" t="s">
         <v>808</v>
@@ -53846,10 +53755,10 @@
         <v>15</v>
       </c>
       <c r="E1992" s="52" t="s">
-        <v>3051</v>
+        <v>11</v>
       </c>
       <c r="F1992" s="52" t="s">
-        <v>3055</v>
+        <v>3042</v>
       </c>
       <c r="G1992" s="52"/>
     </row>
@@ -53858,16 +53767,16 @@
         <v>46279</v>
       </c>
       <c r="C1993" s="52" t="s">
-        <v>3056</v>
+        <v>3043</v>
       </c>
       <c r="D1993" s="52" t="s">
         <v>116</v>
       </c>
       <c r="E1993" s="52" t="s">
-        <v>2942</v>
+        <v>11</v>
       </c>
       <c r="F1993" s="52" t="s">
-        <v>3057</v>
+        <v>3044</v>
       </c>
       <c r="G1993" s="52" t="s">
         <v>34</v>
@@ -53882,13 +53791,13 @@
         <v>492</v>
       </c>
       <c r="D1994" s="54" t="s">
-        <v>3058</v>
-      </c>
-      <c r="E1994" s="54" t="s">
-        <v>2942</v>
+        <v>3045</v>
+      </c>
+      <c r="E1994" s="52" t="s">
+        <v>11</v>
       </c>
       <c r="F1994" s="54" t="s">
-        <v>3059</v>
+        <v>3046</v>
       </c>
       <c r="G1994" s="54" t="s">
         <v>492</v>
@@ -53900,19 +53809,19 @@
         <v>46279</v>
       </c>
       <c r="C1995" s="54" t="s">
-        <v>3060</v>
+        <v>3047</v>
       </c>
       <c r="D1995" s="54" t="s">
-        <v>3061</v>
-      </c>
-      <c r="E1995" s="54" t="s">
-        <v>2942</v>
+        <v>3048</v>
+      </c>
+      <c r="E1995" s="52" t="s">
+        <v>11</v>
       </c>
       <c r="F1995" s="54" t="s">
-        <v>3062</v>
+        <v>3049</v>
       </c>
       <c r="G1995" s="54" t="s">
-        <v>3063</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="1996" spans="2:7" ht="15" customHeight="1">
@@ -53920,16 +53829,16 @@
         <v>46280</v>
       </c>
       <c r="C1996" s="34" t="s">
-        <v>3064</v>
+        <v>3051</v>
       </c>
       <c r="D1996" s="34" t="s">
         <v>1773</v>
       </c>
-      <c r="E1996" s="34" t="s">
-        <v>3065</v>
+      <c r="E1996" s="52" t="s">
+        <v>11</v>
       </c>
       <c r="F1996" s="34" t="s">
-        <v>3066</v>
+        <v>3052</v>
       </c>
       <c r="G1996" s="34" t="s">
         <v>34</v>
@@ -53941,16 +53850,16 @@
         <v>46280</v>
       </c>
       <c r="C1997" s="34" t="s">
-        <v>3004</v>
+        <v>2994</v>
       </c>
       <c r="D1997" s="52" t="s">
         <v>207</v>
       </c>
-      <c r="E1997" s="34" t="s">
-        <v>3065</v>
+      <c r="E1997" s="52" t="s">
+        <v>11</v>
       </c>
       <c r="F1997" s="52" t="s">
-        <v>3067</v>
+        <v>3053</v>
       </c>
       <c r="G1997" s="34" t="s">
         <v>34</v>
@@ -53961,16 +53870,16 @@
         <v>46281</v>
       </c>
       <c r="C1998" s="60" t="s">
-        <v>3068</v>
+        <v>3054</v>
       </c>
       <c r="D1998" s="60" t="s">
         <v>121</v>
       </c>
-      <c r="E1998" s="60" t="s">
-        <v>2992</v>
+      <c r="E1998" s="52" t="s">
+        <v>11</v>
       </c>
       <c r="F1998" s="60" t="s">
-        <v>3069</v>
+        <v>3055</v>
       </c>
       <c r="G1998" s="60" t="s">
         <v>51</v>
@@ -53982,16 +53891,16 @@
         <v>46281</v>
       </c>
       <c r="C1999" s="60" t="s">
-        <v>3070</v>
+        <v>3056</v>
       </c>
       <c r="D1999" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="E1999" s="60" t="s">
-        <v>2992</v>
+      <c r="E1999" s="52" t="s">
+        <v>11</v>
       </c>
       <c r="F1999" s="60" t="s">
-        <v>3071</v>
+        <v>3057</v>
       </c>
       <c r="G1999" s="60" t="s">
         <v>51</v>
@@ -54003,16 +53912,16 @@
         <v>46281</v>
       </c>
       <c r="C2000" s="60" t="s">
-        <v>3072</v>
+        <v>3058</v>
       </c>
       <c r="D2000" s="60" t="s">
         <v>94</v>
       </c>
-      <c r="E2000" s="60" t="s">
-        <v>2992</v>
+      <c r="E2000" s="52" t="s">
+        <v>11</v>
       </c>
       <c r="F2000" s="60" t="s">
-        <v>3073</v>
+        <v>3059</v>
       </c>
       <c r="G2000" s="60" t="s">
         <v>51</v>
@@ -54024,16 +53933,16 @@
         <v>46281</v>
       </c>
       <c r="C2001" s="60" t="s">
-        <v>3074</v>
+        <v>3060</v>
       </c>
       <c r="D2001" s="60" t="s">
         <v>23</v>
       </c>
-      <c r="E2001" s="60" t="s">
-        <v>2992</v>
+      <c r="E2001" s="52" t="s">
+        <v>11</v>
       </c>
       <c r="F2001" s="60" t="s">
-        <v>3075</v>
+        <v>3061</v>
       </c>
       <c r="G2001" s="60" t="s">
         <v>51</v>
@@ -54050,11 +53959,11 @@
       <c r="D2002" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="E2002" s="60" t="s">
-        <v>2992</v>
+      <c r="E2002" s="52" t="s">
+        <v>11</v>
       </c>
       <c r="F2002" s="60" t="s">
-        <v>3076</v>
+        <v>3062</v>
       </c>
       <c r="G2002" s="60" t="s">
         <v>64</v>
@@ -54065,16 +53974,16 @@
         <v>46282</v>
       </c>
       <c r="C2003" s="54" t="s">
-        <v>3077</v>
+        <v>3063</v>
       </c>
       <c r="D2003" s="54" t="s">
         <v>1860</v>
       </c>
-      <c r="E2003" s="54" t="s">
-        <v>2992</v>
+      <c r="E2003" s="52" t="s">
+        <v>11</v>
       </c>
       <c r="F2003" s="54" t="s">
-        <v>3078</v>
+        <v>3064</v>
       </c>
       <c r="G2003" s="54" t="s">
         <v>51</v>
@@ -54086,16 +53995,16 @@
         <v>46282</v>
       </c>
       <c r="C2004" s="54" t="s">
-        <v>3079</v>
+        <v>3065</v>
       </c>
       <c r="D2004" s="54" t="s">
         <v>1860</v>
       </c>
-      <c r="E2004" s="54" t="s">
-        <v>2907</v>
+      <c r="E2004" s="52" t="s">
+        <v>11</v>
       </c>
       <c r="F2004" s="54" t="s">
-        <v>3080</v>
+        <v>3066</v>
       </c>
       <c r="G2004" s="54" t="s">
         <v>51</v>
@@ -54107,16 +54016,16 @@
         <v>46282</v>
       </c>
       <c r="C2005" s="54" t="s">
-        <v>3081</v>
+        <v>3067</v>
       </c>
       <c r="D2005" s="54" t="s">
         <v>859</v>
       </c>
-      <c r="E2005" s="54" t="s">
-        <v>2907</v>
+      <c r="E2005" s="52" t="s">
+        <v>11</v>
       </c>
       <c r="F2005" s="54" t="s">
-        <v>3082</v>
+        <v>3068</v>
       </c>
       <c r="G2005" s="54" t="s">
         <v>51</v>
@@ -54128,16 +54037,16 @@
         <v>46282</v>
       </c>
       <c r="C2006" s="54" t="s">
-        <v>3083</v>
+        <v>3069</v>
       </c>
       <c r="D2006" s="54" t="s">
         <v>23</v>
       </c>
-      <c r="E2006" s="54" t="s">
-        <v>2907</v>
+      <c r="E2006" s="52" t="s">
+        <v>11</v>
       </c>
       <c r="F2006" s="54" t="s">
-        <v>3084</v>
+        <v>3070</v>
       </c>
       <c r="G2006" s="54" t="s">
         <v>51</v>
@@ -54149,13 +54058,13 @@
         <v>46282</v>
       </c>
       <c r="C2007" s="58" t="s">
-        <v>3085</v>
+        <v>3071</v>
       </c>
       <c r="D2007" s="54" t="s">
         <v>1860</v>
       </c>
-      <c r="E2007" s="54" t="s">
-        <v>2907</v>
+      <c r="E2007" s="52" t="s">
+        <v>11</v>
       </c>
       <c r="F2007" s="54" t="s">
         <v>1790</v>
@@ -54170,16 +54079,16 @@
         <v>46282</v>
       </c>
       <c r="C2008" s="54" t="s">
-        <v>3086</v>
+        <v>3072</v>
       </c>
       <c r="D2008" s="54" t="s">
         <v>1860</v>
       </c>
-      <c r="E2008" s="54" t="s">
-        <v>2907</v>
+      <c r="E2008" s="52" t="s">
+        <v>11</v>
       </c>
       <c r="F2008" s="54" t="s">
-        <v>3087</v>
+        <v>3073</v>
       </c>
       <c r="G2008" s="54" t="s">
         <v>51</v>
@@ -54190,16 +54099,16 @@
         <v>46283</v>
       </c>
       <c r="C2009" s="54" t="s">
-        <v>2923</v>
+        <v>2919</v>
       </c>
       <c r="D2009" s="54" t="s">
         <v>462</v>
       </c>
-      <c r="E2009" s="54" t="s">
-        <v>2907</v>
+      <c r="E2009" s="52" t="s">
+        <v>11</v>
       </c>
       <c r="F2009" s="54" t="s">
-        <v>3088</v>
+        <v>3074</v>
       </c>
       <c r="G2009" s="54" t="s">
         <v>51</v>
@@ -54211,16 +54120,16 @@
         <v>46283</v>
       </c>
       <c r="C2010" s="54" t="s">
-        <v>3089</v>
+        <v>3075</v>
       </c>
       <c r="D2010" s="54" t="s">
         <v>42</v>
       </c>
-      <c r="E2010" s="54" t="s">
-        <v>2907</v>
+      <c r="E2010" s="52" t="s">
+        <v>11</v>
       </c>
       <c r="F2010" s="54" t="s">
-        <v>3090</v>
+        <v>3076</v>
       </c>
       <c r="G2010" s="54" t="s">
         <v>51</v>
@@ -54232,16 +54141,16 @@
         <v>46283</v>
       </c>
       <c r="C2011" s="54" t="s">
-        <v>3091</v>
+        <v>3077</v>
       </c>
       <c r="D2011" s="54" t="s">
         <v>202</v>
       </c>
-      <c r="E2011" s="54" t="s">
-        <v>3092</v>
+      <c r="E2011" s="52" t="s">
+        <v>11</v>
       </c>
       <c r="F2011" s="54" t="s">
-        <v>3093</v>
+        <v>3078</v>
       </c>
       <c r="G2011" s="54" t="s">
         <v>92</v>
@@ -54253,16 +54162,16 @@
         <v>46283</v>
       </c>
       <c r="C2012" s="54" t="s">
-        <v>3091</v>
+        <v>3077</v>
       </c>
       <c r="D2012" s="54" t="s">
         <v>42</v>
       </c>
-      <c r="E2012" s="54" t="s">
-        <v>3092</v>
+      <c r="E2012" s="52" t="s">
+        <v>11</v>
       </c>
       <c r="F2012" s="54" t="s">
-        <v>3094</v>
+        <v>3079</v>
       </c>
       <c r="G2012" s="54" t="s">
         <v>51</v>
@@ -54274,19 +54183,19 @@
         <v>46283</v>
       </c>
       <c r="C2013" s="58" t="s">
-        <v>3095</v>
+        <v>3080</v>
       </c>
       <c r="D2013" s="54" t="s">
         <v>1166</v>
       </c>
-      <c r="E2013" s="54" t="s">
-        <v>3092</v>
+      <c r="E2013" s="52" t="s">
+        <v>11</v>
       </c>
       <c r="F2013" s="54" t="s">
-        <v>3096</v>
+        <v>3081</v>
       </c>
       <c r="G2013" s="54" t="s">
-        <v>3097</v>
+        <v>3082</v>
       </c>
     </row>
     <row r="2014" spans="2:7" ht="15" customHeight="1">
@@ -54295,16 +54204,16 @@
         <v>46283</v>
       </c>
       <c r="C2014" s="54" t="s">
-        <v>3098</v>
+        <v>3083</v>
       </c>
       <c r="D2014" s="54" t="s">
         <v>352</v>
       </c>
-      <c r="E2014" s="54" t="s">
-        <v>3092</v>
+      <c r="E2014" s="52" t="s">
+        <v>11</v>
       </c>
       <c r="F2014" s="54" t="s">
-        <v>3099</v>
+        <v>3084</v>
       </c>
       <c r="G2014" s="54" t="s">
         <v>92</v>
@@ -54321,11 +54230,11 @@
       <c r="D2015" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="E2015" s="54" t="s">
-        <v>3092</v>
+      <c r="E2015" s="52" t="s">
+        <v>11</v>
       </c>
       <c r="F2015" s="54" t="s">
-        <v>3100</v>
+        <v>3085</v>
       </c>
       <c r="G2015" s="54" t="s">
         <v>92</v>
@@ -54337,16 +54246,16 @@
         <v>46283</v>
       </c>
       <c r="C2016" s="54" t="s">
-        <v>3091</v>
+        <v>3077</v>
       </c>
       <c r="D2016" s="54" t="s">
         <v>76</v>
       </c>
-      <c r="E2016" s="54" t="s">
-        <v>3092</v>
+      <c r="E2016" s="52" t="s">
+        <v>11</v>
       </c>
       <c r="F2016" s="54" t="s">
-        <v>3101</v>
+        <v>3086</v>
       </c>
       <c r="G2016" s="54" t="s">
         <v>92</v>
@@ -54361,13 +54270,13 @@
         <v>92</v>
       </c>
       <c r="D2017" s="54" t="s">
-        <v>3102</v>
-      </c>
-      <c r="E2017" s="54" t="s">
-        <v>3092</v>
+        <v>3087</v>
+      </c>
+      <c r="E2017" s="52" t="s">
+        <v>11</v>
       </c>
       <c r="F2017" s="54" t="s">
-        <v>3103</v>
+        <v>3088</v>
       </c>
       <c r="G2017" s="54" t="s">
         <v>92</v>
@@ -54384,14 +54293,14 @@
       <c r="D2018" s="54" t="s">
         <v>261</v>
       </c>
-      <c r="E2018" s="54" t="s">
-        <v>3092</v>
+      <c r="E2018" s="52" t="s">
+        <v>11</v>
       </c>
       <c r="F2018" s="62" t="s">
-        <v>3104</v>
+        <v>3089</v>
       </c>
       <c r="G2018" s="54" t="s">
-        <v>3105</v>
+        <v>3090</v>
       </c>
     </row>
     <row r="2019" spans="2:7" ht="15" customHeight="1">
@@ -54400,19 +54309,19 @@
         <v>46283</v>
       </c>
       <c r="C2019" s="54" t="s">
-        <v>3106</v>
+        <v>3091</v>
       </c>
       <c r="D2019" s="54" t="s">
         <v>261</v>
       </c>
-      <c r="E2019" s="54" t="s">
+      <c r="E2019" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2019" s="62" t="s">
         <v>3092</v>
       </c>
-      <c r="F2019" s="62" t="s">
-        <v>3107</v>
-      </c>
       <c r="G2019" s="54" t="s">
-        <v>3106</v>
+        <v>3091</v>
       </c>
     </row>
     <row r="2020" spans="2:7" ht="15" customHeight="1">
@@ -54420,16 +54329,16 @@
         <v>46284</v>
       </c>
       <c r="C2020" s="52" t="s">
-        <v>3091</v>
+        <v>3077</v>
       </c>
       <c r="D2020" s="52" t="s">
         <v>81</v>
       </c>
       <c r="E2020" s="52" t="s">
-        <v>3092</v>
+        <v>11</v>
       </c>
       <c r="F2020" s="52" t="s">
-        <v>3108</v>
+        <v>3093</v>
       </c>
       <c r="G2020" s="52" t="s">
         <v>105</v>
@@ -54447,10 +54356,10 @@
         <v>2365</v>
       </c>
       <c r="E2021" s="52" t="s">
-        <v>3092</v>
+        <v>11</v>
       </c>
       <c r="F2021" s="52" t="s">
-        <v>3109</v>
+        <v>3094</v>
       </c>
       <c r="G2021" s="52" t="s">
         <v>105</v>
@@ -54468,10 +54377,10 @@
         <v>52</v>
       </c>
       <c r="E2022" s="52" t="s">
-        <v>3110</v>
+        <v>28</v>
       </c>
       <c r="F2022" s="52" t="s">
-        <v>3111</v>
+        <v>3095</v>
       </c>
       <c r="G2022" s="52" t="s">
         <v>30</v>
@@ -54483,16 +54392,16 @@
         <v>46284</v>
       </c>
       <c r="C2023" s="52" t="s">
-        <v>3112</v>
+        <v>3096</v>
       </c>
       <c r="D2023" s="52" t="s">
         <v>385</v>
       </c>
       <c r="E2023" s="52" t="s">
-        <v>3110</v>
+        <v>28</v>
       </c>
       <c r="F2023" s="52" t="s">
-        <v>3113</v>
+        <v>3097</v>
       </c>
       <c r="G2023" s="52" t="s">
         <v>662</v>
@@ -54510,10 +54419,10 @@
         <v>52</v>
       </c>
       <c r="E2024" s="52" t="s">
-        <v>3110</v>
+        <v>28</v>
       </c>
       <c r="F2024" s="52" t="s">
-        <v>3114</v>
+        <v>3098</v>
       </c>
       <c r="G2024" s="52" t="s">
         <v>2874</v>
@@ -54525,13 +54434,13 @@
         <v>46284</v>
       </c>
       <c r="C2025" s="52" t="s">
-        <v>3115</v>
+        <v>3099</v>
       </c>
       <c r="D2025" s="52" t="s">
         <v>456</v>
       </c>
       <c r="E2025" s="52" t="s">
-        <v>3110</v>
+        <v>28</v>
       </c>
       <c r="F2025" s="52" t="s">
         <v>1327</v>
@@ -54552,10 +54461,10 @@
         <v>81</v>
       </c>
       <c r="E2026" s="52" t="s">
-        <v>3110</v>
+        <v>28</v>
       </c>
       <c r="F2026" s="52" t="s">
-        <v>3116</v>
+        <v>3100</v>
       </c>
       <c r="G2026" s="52" t="s">
         <v>2874</v>
@@ -54567,16 +54476,16 @@
         <v>46284</v>
       </c>
       <c r="C2027" s="52" t="s">
-        <v>3117</v>
+        <v>3101</v>
       </c>
       <c r="D2027" s="52" t="s">
         <v>62</v>
       </c>
       <c r="E2027" s="52" t="s">
-        <v>3110</v>
+        <v>28</v>
       </c>
       <c r="F2027" s="52" t="s">
-        <v>3118</v>
+        <v>3102</v>
       </c>
       <c r="G2027" s="52" t="s">
         <v>187</v>
@@ -54594,7 +54503,7 @@
         <v>1935</v>
       </c>
       <c r="E2028" s="52" t="s">
-        <v>3110</v>
+        <v>28</v>
       </c>
       <c r="F2028" s="52" t="s">
         <v>1413</v>
@@ -54615,13 +54524,13 @@
         <v>385</v>
       </c>
       <c r="E2029" s="52" t="s">
-        <v>3110</v>
+        <v>28</v>
       </c>
       <c r="F2029" s="53" t="s">
         <v>578</v>
       </c>
       <c r="G2029" s="52" t="s">
-        <v>3119</v>
+        <v>3103</v>
       </c>
     </row>
     <row r="2030" spans="2:7" ht="15" customHeight="1">
@@ -54636,13 +54545,13 @@
         <v>389</v>
       </c>
       <c r="E2030" s="52" t="s">
-        <v>3110</v>
+        <v>28</v>
       </c>
       <c r="F2030" s="53" t="s">
-        <v>3120</v>
+        <v>3104</v>
       </c>
       <c r="G2030" s="52" t="s">
-        <v>3119</v>
+        <v>3103</v>
       </c>
     </row>
     <row r="2031" spans="2:7" ht="15" customHeight="1">
@@ -54651,16 +54560,16 @@
         <v>46284</v>
       </c>
       <c r="C2031" s="52" t="s">
-        <v>3121</v>
+        <v>3105</v>
       </c>
       <c r="D2031" s="52" t="s">
         <v>385</v>
       </c>
       <c r="E2031" s="52" t="s">
-        <v>3110</v>
+        <v>28</v>
       </c>
       <c r="F2031" s="53" t="s">
-        <v>3122</v>
+        <v>3106</v>
       </c>
       <c r="G2031" s="52" t="s">
         <v>187</v>
@@ -54672,16 +54581,16 @@
         <v>46284</v>
       </c>
       <c r="C2032" s="52" t="s">
-        <v>3123</v>
+        <v>3107</v>
       </c>
       <c r="D2032" s="52" t="s">
         <v>716</v>
       </c>
       <c r="E2032" s="52" t="s">
-        <v>3110</v>
+        <v>28</v>
       </c>
       <c r="F2032" s="53" t="s">
-        <v>3124</v>
+        <v>3108</v>
       </c>
       <c r="G2032" s="52" t="s">
         <v>187</v>
@@ -54693,16 +54602,16 @@
         <v>46284</v>
       </c>
       <c r="C2033" s="52" t="s">
-        <v>3117</v>
+        <v>3101</v>
       </c>
       <c r="D2033" s="52" t="s">
         <v>385</v>
       </c>
       <c r="E2033" s="52" t="s">
-        <v>3110</v>
+        <v>28</v>
       </c>
       <c r="F2033" s="52" t="s">
-        <v>3118</v>
+        <v>3102</v>
       </c>
       <c r="G2033" s="52" t="s">
         <v>662</v>
@@ -54714,16 +54623,16 @@
         <v>46284</v>
       </c>
       <c r="C2034" s="52" t="s">
-        <v>3125</v>
+        <v>3109</v>
       </c>
       <c r="D2034" s="52" t="s">
         <v>462</v>
       </c>
       <c r="E2034" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2034" s="53" t="s">
         <v>3110</v>
-      </c>
-      <c r="F2034" s="53" t="s">
-        <v>3126</v>
       </c>
       <c r="G2034" s="52" t="s">
         <v>187</v>
@@ -54735,16 +54644,16 @@
         <v>46284</v>
       </c>
       <c r="C2035" s="52" t="s">
-        <v>3127</v>
+        <v>3111</v>
       </c>
       <c r="D2035" s="52" t="s">
         <v>459</v>
       </c>
       <c r="E2035" s="52" t="s">
-        <v>3110</v>
+        <v>28</v>
       </c>
       <c r="F2035" s="53" t="s">
-        <v>3128</v>
+        <v>3112</v>
       </c>
       <c r="G2035" s="52" t="s">
         <v>662</v>
@@ -54756,16 +54665,16 @@
         <v>46284</v>
       </c>
       <c r="C2036" s="52" t="s">
-        <v>3129</v>
+        <v>3113</v>
       </c>
       <c r="D2036" s="52" t="s">
         <v>456</v>
       </c>
       <c r="E2036" s="52" t="s">
-        <v>3110</v>
+        <v>28</v>
       </c>
       <c r="F2036" s="52" t="s">
-        <v>3130</v>
+        <v>3114</v>
       </c>
       <c r="G2036" s="52" t="s">
         <v>187</v>
@@ -54777,16 +54686,16 @@
         <v>46284</v>
       </c>
       <c r="C2037" s="52" t="s">
-        <v>3131</v>
+        <v>3115</v>
       </c>
       <c r="D2037" s="52" t="s">
         <v>385</v>
       </c>
       <c r="E2037" s="52" t="s">
-        <v>3110</v>
+        <v>28</v>
       </c>
       <c r="F2037" s="52" t="s">
-        <v>3132</v>
+        <v>3116</v>
       </c>
       <c r="G2037" s="52" t="s">
         <v>187</v>
@@ -54804,10 +54713,10 @@
         <v>62</v>
       </c>
       <c r="E2038" s="52" t="s">
-        <v>3110</v>
+        <v>28</v>
       </c>
       <c r="F2038" s="52" t="s">
-        <v>3133</v>
+        <v>3117</v>
       </c>
       <c r="G2038" s="52" t="s">
         <v>371</v>
@@ -54825,10 +54734,10 @@
         <v>213</v>
       </c>
       <c r="E2039" s="52" t="s">
-        <v>3110</v>
+        <v>28</v>
       </c>
       <c r="F2039" s="52" t="s">
-        <v>3133</v>
+        <v>3117</v>
       </c>
       <c r="G2039" s="52" t="s">
         <v>371</v>
@@ -54845,10 +54754,10 @@
         <v>44</v>
       </c>
       <c r="E2040" s="52" t="s">
-        <v>3134</v>
+        <v>28</v>
       </c>
       <c r="F2040" s="52" t="s">
-        <v>3135</v>
+        <v>3118</v>
       </c>
       <c r="G2040" s="52" t="s">
         <v>70</v>
@@ -54866,7 +54775,7 @@
         <v>62</v>
       </c>
       <c r="E2041" s="52" t="s">
-        <v>3134</v>
+        <v>28</v>
       </c>
       <c r="F2041" s="52" t="s">
         <v>578</v>
@@ -54881,16 +54790,16 @@
         <v>46285</v>
       </c>
       <c r="C2042" s="52" t="s">
-        <v>3136</v>
+        <v>3119</v>
       </c>
       <c r="D2042" s="52" t="s">
         <v>52</v>
       </c>
       <c r="E2042" s="52" t="s">
-        <v>3134</v>
+        <v>28</v>
       </c>
       <c r="F2042" s="52" t="s">
-        <v>3137</v>
+        <v>3120</v>
       </c>
       <c r="G2042" s="52" t="s">
         <v>83</v>
@@ -54902,16 +54811,16 @@
         <v>46285</v>
       </c>
       <c r="C2043" s="52" t="s">
-        <v>3138</v>
+        <v>3121</v>
       </c>
       <c r="D2043" s="52" t="s">
         <v>796</v>
       </c>
       <c r="E2043" s="52" t="s">
-        <v>3134</v>
+        <v>28</v>
       </c>
       <c r="F2043" s="52" t="s">
-        <v>3139</v>
+        <v>3122</v>
       </c>
       <c r="G2043" s="52" t="s">
         <v>2874</v>
@@ -54923,16 +54832,16 @@
         <v>46285</v>
       </c>
       <c r="C2044" s="52" t="s">
-        <v>3140</v>
+        <v>3123</v>
       </c>
       <c r="D2044" s="52" t="s">
         <v>44</v>
       </c>
       <c r="E2044" s="52" t="s">
-        <v>3134</v>
+        <v>28</v>
       </c>
       <c r="F2044" s="52" t="s">
-        <v>3141</v>
+        <v>3124</v>
       </c>
       <c r="G2044" s="52" t="s">
         <v>70</v>
@@ -54944,16 +54853,16 @@
         <v>46285</v>
       </c>
       <c r="C2045" s="52" t="s">
-        <v>3142</v>
+        <v>3125</v>
       </c>
       <c r="D2045" s="52" t="s">
         <v>19</v>
       </c>
       <c r="E2045" s="52" t="s">
-        <v>3134</v>
+        <v>28</v>
       </c>
       <c r="F2045" s="52" t="s">
-        <v>3143</v>
+        <v>3126</v>
       </c>
       <c r="G2045" s="52" t="s">
         <v>83</v>
@@ -54971,10 +54880,10 @@
         <v>44</v>
       </c>
       <c r="E2046" s="52" t="s">
-        <v>3134</v>
+        <v>28</v>
       </c>
       <c r="F2046" s="52" t="s">
-        <v>3144</v>
+        <v>3127</v>
       </c>
       <c r="G2046" s="52" t="s">
         <v>70</v>
@@ -54986,16 +54895,16 @@
         <v>46285</v>
       </c>
       <c r="C2047" s="52" t="s">
-        <v>3145</v>
+        <v>3128</v>
       </c>
       <c r="D2047" s="52" t="s">
         <v>52</v>
       </c>
       <c r="E2047" s="52" t="s">
-        <v>3134</v>
+        <v>28</v>
       </c>
       <c r="F2047" s="52" t="s">
-        <v>3120</v>
+        <v>3104</v>
       </c>
       <c r="G2047" s="52" t="s">
         <v>2874</v>
@@ -55013,10 +54922,10 @@
         <v>44</v>
       </c>
       <c r="E2048" s="52" t="s">
-        <v>3134</v>
+        <v>28</v>
       </c>
       <c r="F2048" s="52" t="s">
-        <v>3146</v>
+        <v>3129</v>
       </c>
       <c r="G2048" s="52" t="s">
         <v>70</v>
@@ -55028,16 +54937,16 @@
         <v>46285</v>
       </c>
       <c r="C2049" s="52" t="s">
-        <v>3147</v>
+        <v>3130</v>
       </c>
       <c r="D2049" s="52" t="s">
-        <v>3148</v>
+        <v>3131</v>
       </c>
       <c r="E2049" s="52" t="s">
-        <v>3134</v>
+        <v>28</v>
       </c>
       <c r="F2049" s="53" t="s">
-        <v>3149</v>
+        <v>3132</v>
       </c>
       <c r="G2049" s="52" t="s">
         <v>187</v>
@@ -55055,10 +54964,10 @@
         <v>456</v>
       </c>
       <c r="E2050" s="52" t="s">
-        <v>3134</v>
+        <v>28</v>
       </c>
       <c r="F2050" s="53" t="s">
-        <v>3150</v>
+        <v>3133</v>
       </c>
       <c r="G2050" s="52" t="s">
         <v>187</v>
@@ -55076,10 +54985,10 @@
         <v>385</v>
       </c>
       <c r="E2051" s="52" t="s">
-        <v>3151</v>
+        <v>11</v>
       </c>
       <c r="F2051" s="52" t="s">
-        <v>3152</v>
+        <v>3134</v>
       </c>
       <c r="G2051" s="52" t="s">
         <v>41</v>
@@ -55091,16 +55000,16 @@
         <v>46285</v>
       </c>
       <c r="C2052" s="52" t="s">
-        <v>3153</v>
+        <v>3135</v>
       </c>
       <c r="D2052" s="52" t="s">
         <v>62</v>
       </c>
       <c r="E2052" s="52" t="s">
-        <v>3151</v>
+        <v>11</v>
       </c>
       <c r="F2052" s="53" t="s">
-        <v>3154</v>
+        <v>3136</v>
       </c>
       <c r="G2052" s="52" t="s">
         <v>83</v>
@@ -55112,16 +55021,16 @@
         <v>46285</v>
       </c>
       <c r="C2053" s="52" t="s">
-        <v>3155</v>
+        <v>3137</v>
       </c>
       <c r="D2053" s="52" t="s">
         <v>256</v>
       </c>
       <c r="E2053" s="52" t="s">
-        <v>3151</v>
+        <v>11</v>
       </c>
       <c r="F2053" s="52" t="s">
-        <v>3156</v>
+        <v>3138</v>
       </c>
       <c r="G2053" s="52" t="s">
         <v>51</v>
@@ -55133,16 +55042,16 @@
         <v>46285</v>
       </c>
       <c r="C2054" s="52" t="s">
-        <v>3157</v>
+        <v>3139</v>
       </c>
       <c r="D2054" s="52" t="s">
         <v>385</v>
       </c>
       <c r="E2054" s="52" t="s">
-        <v>3151</v>
+        <v>11</v>
       </c>
       <c r="F2054" s="52" t="s">
-        <v>3158</v>
+        <v>3140</v>
       </c>
       <c r="G2054" s="52" t="s">
         <v>51</v>
@@ -55154,13 +55063,13 @@
         <v>46285</v>
       </c>
       <c r="C2055" s="52" t="s">
-        <v>3159</v>
+        <v>3141</v>
       </c>
       <c r="D2055" s="52" t="s">
         <v>44</v>
       </c>
       <c r="E2055" s="52" t="s">
-        <v>3151</v>
+        <v>11</v>
       </c>
       <c r="F2055" s="52" t="s">
         <v>2860</v>
@@ -55175,16 +55084,16 @@
         <v>46285</v>
       </c>
       <c r="C2056" s="52" t="s">
-        <v>3160</v>
+        <v>3142</v>
       </c>
       <c r="D2056" s="52" t="s">
         <v>633</v>
       </c>
       <c r="E2056" s="52" t="s">
-        <v>3151</v>
+        <v>11</v>
       </c>
       <c r="F2056" s="52" t="s">
-        <v>3161</v>
+        <v>3143</v>
       </c>
       <c r="G2056" s="52" t="s">
         <v>51</v>
@@ -55196,16 +55105,16 @@
         <v>46285</v>
       </c>
       <c r="C2057" s="52" t="s">
-        <v>3153</v>
+        <v>3135</v>
       </c>
       <c r="D2057" s="52" t="s">
         <v>19</v>
       </c>
       <c r="E2057" s="52" t="s">
-        <v>3151</v>
+        <v>11</v>
       </c>
       <c r="F2057" s="33" t="s">
-        <v>3162</v>
+        <v>3144</v>
       </c>
       <c r="G2057" s="52" t="s">
         <v>83</v>
@@ -55217,16 +55126,16 @@
         <v>46285</v>
       </c>
       <c r="C2058" s="52" t="s">
-        <v>3163</v>
+        <v>3145</v>
       </c>
       <c r="D2058" s="52" t="s">
         <v>62</v>
       </c>
       <c r="E2058" s="52" t="s">
-        <v>3151</v>
+        <v>11</v>
       </c>
       <c r="F2058" s="52" t="s">
-        <v>3164</v>
+        <v>3146</v>
       </c>
       <c r="G2058" s="52" t="s">
         <v>51</v>
@@ -55238,16 +55147,16 @@
         <v>46285</v>
       </c>
       <c r="C2059" s="52" t="s">
-        <v>3165</v>
+        <v>3147</v>
       </c>
       <c r="D2059" s="52" t="s">
         <v>507</v>
       </c>
       <c r="E2059" s="52" t="s">
-        <v>3151</v>
+        <v>11</v>
       </c>
       <c r="F2059" s="52" t="s">
-        <v>3166</v>
+        <v>3148</v>
       </c>
       <c r="G2059" s="52" t="s">
         <v>51</v>
@@ -55259,16 +55168,16 @@
         <v>46285</v>
       </c>
       <c r="C2060" s="52" t="s">
-        <v>3167</v>
+        <v>3149</v>
       </c>
       <c r="D2060" s="52" t="s">
         <v>44</v>
       </c>
       <c r="E2060" s="52" t="s">
-        <v>3151</v>
+        <v>11</v>
       </c>
       <c r="F2060" s="52" t="s">
-        <v>3168</v>
+        <v>3150</v>
       </c>
       <c r="G2060" s="52" t="s">
         <v>51</v>
@@ -55279,16 +55188,16 @@
         <v>46286</v>
       </c>
       <c r="C2061" s="52" t="s">
-        <v>3169</v>
+        <v>3151</v>
       </c>
       <c r="D2061" s="52" t="s">
-        <v>3170</v>
+        <v>3152</v>
       </c>
       <c r="E2061" s="52" t="s">
-        <v>3151</v>
+        <v>11</v>
       </c>
       <c r="F2061" s="52" t="s">
-        <v>3171</v>
+        <v>3153</v>
       </c>
       <c r="G2061" s="52" t="s">
         <v>51</v>
@@ -55299,16 +55208,16 @@
         <v>46286</v>
       </c>
       <c r="C2062" s="52" t="s">
-        <v>3172</v>
+        <v>3154</v>
       </c>
       <c r="D2062" s="52" t="s">
         <v>385</v>
       </c>
       <c r="E2062" s="52" t="s">
-        <v>3151</v>
+        <v>11</v>
       </c>
       <c r="F2062" s="52" t="s">
-        <v>3173</v>
+        <v>3155</v>
       </c>
       <c r="G2062" s="52" t="s">
         <v>51</v>
@@ -55319,16 +55228,16 @@
         <v>46286</v>
       </c>
       <c r="C2063" s="52" t="s">
-        <v>3174</v>
+        <v>3156</v>
       </c>
       <c r="D2063" s="52" t="s">
         <v>394</v>
       </c>
       <c r="E2063" s="52" t="s">
-        <v>2907</v>
+        <v>11</v>
       </c>
       <c r="F2063" s="52" t="s">
-        <v>3175</v>
+        <v>3157</v>
       </c>
       <c r="G2063" s="52" t="s">
         <v>51</v>
@@ -55339,16 +55248,16 @@
         <v>46286</v>
       </c>
       <c r="C2064" s="52" t="s">
-        <v>3176</v>
+        <v>3158</v>
       </c>
       <c r="D2064" s="52" t="s">
         <v>385</v>
       </c>
       <c r="E2064" s="52" t="s">
-        <v>2907</v>
+        <v>11</v>
       </c>
       <c r="F2064" s="52" t="s">
-        <v>3177</v>
+        <v>3159</v>
       </c>
       <c r="G2064" s="52" t="s">
         <v>51</v>
@@ -55359,16 +55268,16 @@
         <v>46286</v>
       </c>
       <c r="C2065" s="52" t="s">
-        <v>3178</v>
+        <v>3160</v>
       </c>
       <c r="D2065" s="52" t="s">
         <v>1860</v>
       </c>
       <c r="E2065" s="52" t="s">
-        <v>2907</v>
+        <v>11</v>
       </c>
       <c r="F2065" s="52" t="s">
-        <v>3179</v>
+        <v>3161</v>
       </c>
       <c r="G2065" s="52" t="s">
         <v>51</v>
@@ -55379,16 +55288,16 @@
         <v>46286</v>
       </c>
       <c r="C2066" s="52" t="s">
-        <v>3180</v>
+        <v>3162</v>
       </c>
       <c r="D2066" s="52" t="s">
         <v>459</v>
       </c>
       <c r="E2066" s="52" t="s">
-        <v>2907</v>
+        <v>11</v>
       </c>
       <c r="F2066" s="52" t="s">
-        <v>3181</v>
+        <v>3163</v>
       </c>
       <c r="G2066" s="52" t="s">
         <v>51</v>
@@ -55399,16 +55308,16 @@
         <v>46286</v>
       </c>
       <c r="C2067" s="52" t="s">
-        <v>3182</v>
+        <v>3164</v>
       </c>
       <c r="D2067" s="52" t="s">
         <v>1860</v>
       </c>
       <c r="E2067" s="52" t="s">
-        <v>2907</v>
+        <v>11</v>
       </c>
       <c r="F2067" s="52" t="s">
-        <v>3183</v>
+        <v>3165</v>
       </c>
       <c r="G2067" s="52" t="s">
         <v>51</v>
@@ -55419,16 +55328,16 @@
         <v>46286</v>
       </c>
       <c r="C2068" s="52" t="s">
-        <v>3184</v>
+        <v>3166</v>
       </c>
       <c r="D2068" s="52" t="s">
         <v>52</v>
       </c>
       <c r="E2068" s="52" t="s">
-        <v>2907</v>
+        <v>11</v>
       </c>
       <c r="F2068" s="52" t="s">
-        <v>3185</v>
+        <v>3167</v>
       </c>
       <c r="G2068" s="52" t="s">
         <v>51</v>
@@ -55439,16 +55348,16 @@
         <v>46286</v>
       </c>
       <c r="C2069" s="52" t="s">
-        <v>3186</v>
+        <v>3168</v>
       </c>
       <c r="D2069" s="52" t="s">
         <v>38</v>
       </c>
       <c r="E2069" s="52" t="s">
-        <v>2907</v>
+        <v>11</v>
       </c>
       <c r="F2069" s="52" t="s">
-        <v>3187</v>
+        <v>3169</v>
       </c>
       <c r="G2069" s="52" t="s">
         <v>51</v>
@@ -55459,13 +55368,13 @@
         <v>46287</v>
       </c>
       <c r="C2070" s="52" t="s">
-        <v>3188</v>
+        <v>3170</v>
       </c>
       <c r="D2070" s="52" t="s">
         <v>42</v>
       </c>
       <c r="E2070" s="52" t="s">
-        <v>2907</v>
+        <v>11</v>
       </c>
       <c r="F2070" s="52" t="s">
         <v>1973</v>
@@ -55479,16 +55388,16 @@
         <v>46287</v>
       </c>
       <c r="C2071" s="52" t="s">
-        <v>3189</v>
+        <v>3171</v>
       </c>
       <c r="D2071" s="52" t="s">
         <v>42</v>
       </c>
       <c r="E2071" s="52" t="s">
-        <v>2907</v>
+        <v>11</v>
       </c>
       <c r="F2071" s="52" t="s">
-        <v>3190</v>
+        <v>3172</v>
       </c>
       <c r="G2071" s="52" t="s">
         <v>51</v>
@@ -55499,16 +55408,16 @@
         <v>46287</v>
       </c>
       <c r="C2072" s="52" t="s">
-        <v>3191</v>
+        <v>3173</v>
       </c>
       <c r="D2072" s="52" t="s">
-        <v>3192</v>
+        <v>3174</v>
       </c>
       <c r="E2072" s="52" t="s">
-        <v>2907</v>
+        <v>11</v>
       </c>
       <c r="F2072" s="52" t="s">
-        <v>3193</v>
+        <v>3175</v>
       </c>
       <c r="G2072" s="52" t="s">
         <v>51</v>
@@ -55525,10 +55434,10 @@
         <v>261</v>
       </c>
       <c r="E2073" s="52" t="s">
-        <v>3194</v>
+        <v>28</v>
       </c>
       <c r="F2073" s="52" t="s">
-        <v>3195</v>
+        <v>3176</v>
       </c>
       <c r="G2073" s="52" t="s">
         <v>30</v>
@@ -55539,16 +55448,16 @@
         <v>46287</v>
       </c>
       <c r="C2074" s="52" t="s">
-        <v>3196</v>
+        <v>3177</v>
       </c>
       <c r="D2074" s="52" t="s">
         <v>403</v>
       </c>
       <c r="E2074" s="52" t="s">
-        <v>3194</v>
+        <v>28</v>
       </c>
       <c r="F2074" s="52" t="s">
-        <v>3197</v>
+        <v>3178</v>
       </c>
       <c r="G2074" s="52" t="s">
         <v>51</v>
@@ -55559,16 +55468,16 @@
         <v>46287</v>
       </c>
       <c r="C2075" s="52" t="s">
-        <v>3198</v>
+        <v>3179</v>
       </c>
       <c r="D2075" s="52" t="s">
         <v>62</v>
       </c>
       <c r="E2075" s="52" t="s">
-        <v>3194</v>
+        <v>28</v>
       </c>
       <c r="F2075" s="52" t="s">
-        <v>3199</v>
+        <v>3180</v>
       </c>
       <c r="G2075" s="52" t="s">
         <v>51</v>
@@ -55585,10 +55494,10 @@
         <v>596</v>
       </c>
       <c r="E2076" s="52" t="s">
-        <v>3194</v>
+        <v>28</v>
       </c>
       <c r="F2076" s="52" t="s">
-        <v>3200</v>
+        <v>3181</v>
       </c>
       <c r="G2076" s="52" t="s">
         <v>30</v>
@@ -55605,10 +55514,10 @@
         <v>834</v>
       </c>
       <c r="E2077" s="52" t="s">
-        <v>3194</v>
+        <v>28</v>
       </c>
       <c r="F2077" s="52" t="s">
-        <v>3201</v>
+        <v>3182</v>
       </c>
       <c r="G2077" s="52" t="s">
         <v>371</v>
@@ -55625,10 +55534,10 @@
         <v>456</v>
       </c>
       <c r="E2078" s="52" t="s">
-        <v>3194</v>
+        <v>28</v>
       </c>
       <c r="F2078" s="52" t="s">
-        <v>3202</v>
+        <v>3183</v>
       </c>
       <c r="G2078" s="52" t="s">
         <v>30</v>
@@ -55645,10 +55554,10 @@
         <v>2754</v>
       </c>
       <c r="E2079" s="52" t="s">
-        <v>3194</v>
+        <v>28</v>
       </c>
       <c r="F2079" s="52" t="s">
-        <v>3203</v>
+        <v>3184</v>
       </c>
       <c r="G2079" s="52" t="s">
         <v>70</v>
@@ -55665,10 +55574,10 @@
         <v>103</v>
       </c>
       <c r="E2080" s="52" t="s">
-        <v>3194</v>
+        <v>28</v>
       </c>
       <c r="F2080" s="52" t="s">
-        <v>3204</v>
+        <v>3185</v>
       </c>
       <c r="G2080" s="52" t="s">
         <v>70</v>
@@ -55685,7 +55594,7 @@
         <v>352</v>
       </c>
       <c r="E2081" s="52" t="s">
-        <v>3194</v>
+        <v>28</v>
       </c>
       <c r="F2081" s="52" t="s">
         <v>312</v>
@@ -55705,10 +55614,10 @@
         <v>94</v>
       </c>
       <c r="E2082" s="52" t="s">
-        <v>3194</v>
+        <v>28</v>
       </c>
       <c r="F2082" s="52" t="s">
-        <v>3205</v>
+        <v>3186</v>
       </c>
       <c r="G2082" s="52" t="s">
         <v>237</v>
@@ -55719,16 +55628,16 @@
         <v>46287</v>
       </c>
       <c r="C2083" s="52" t="s">
-        <v>3198</v>
+        <v>3179</v>
       </c>
       <c r="D2083" s="52" t="s">
         <v>44</v>
       </c>
       <c r="E2083" s="52" t="s">
-        <v>3194</v>
+        <v>28</v>
       </c>
       <c r="F2083" s="52" t="s">
-        <v>3206</v>
+        <v>3187</v>
       </c>
       <c r="G2083" s="52" t="s">
         <v>51</v>
@@ -55745,10 +55654,10 @@
         <v>44</v>
       </c>
       <c r="E2084" s="52" t="s">
-        <v>3194</v>
+        <v>28</v>
       </c>
       <c r="F2084" s="52" t="s">
-        <v>3207</v>
+        <v>3188</v>
       </c>
       <c r="G2084" s="52" t="s">
         <v>30</v>
@@ -55759,16 +55668,16 @@
         <v>46287</v>
       </c>
       <c r="C2085" s="52" t="s">
-        <v>3196</v>
+        <v>3177</v>
       </c>
       <c r="D2085" s="52" t="s">
         <v>910</v>
       </c>
       <c r="E2085" s="52" t="s">
-        <v>3194</v>
+        <v>28</v>
       </c>
       <c r="F2085" s="52" t="s">
-        <v>3208</v>
+        <v>3189</v>
       </c>
       <c r="G2085" s="52" t="s">
         <v>51</v>
@@ -55785,7 +55694,7 @@
         <v>62</v>
       </c>
       <c r="E2086" s="52" t="s">
-        <v>3194</v>
+        <v>28</v>
       </c>
       <c r="F2086" s="52" t="s">
         <v>2617</v>
@@ -55805,10 +55714,10 @@
         <v>10</v>
       </c>
       <c r="E2087" s="52" t="s">
-        <v>3194</v>
+        <v>28</v>
       </c>
       <c r="F2087" s="52" t="s">
-        <v>3209</v>
+        <v>3190</v>
       </c>
       <c r="G2087" s="52" t="s">
         <v>70</v>
@@ -55825,10 +55734,10 @@
         <v>459</v>
       </c>
       <c r="E2088" s="52" t="s">
-        <v>3210</v>
+        <v>11</v>
       </c>
       <c r="F2088" s="52" t="s">
-        <v>3211</v>
+        <v>3191</v>
       </c>
       <c r="G2088" s="52" t="s">
         <v>70</v>
@@ -55839,16 +55748,16 @@
         <v>46287</v>
       </c>
       <c r="C2089" s="52" t="s">
-        <v>3212</v>
+        <v>3192</v>
       </c>
       <c r="D2089" s="52" t="s">
         <v>44</v>
       </c>
       <c r="E2089" s="52" t="s">
-        <v>3210</v>
+        <v>11</v>
       </c>
       <c r="F2089" s="52" t="s">
-        <v>3213</v>
+        <v>3193</v>
       </c>
       <c r="G2089" s="52" t="s">
         <v>70</v>
@@ -55859,16 +55768,16 @@
         <v>46287</v>
       </c>
       <c r="C2090" s="52" t="s">
-        <v>3214</v>
+        <v>3194</v>
       </c>
       <c r="D2090" s="52" t="s">
         <v>570</v>
       </c>
       <c r="E2090" s="52" t="s">
-        <v>3210</v>
+        <v>11</v>
       </c>
       <c r="F2090" s="53" t="s">
-        <v>3215</v>
+        <v>3195</v>
       </c>
       <c r="G2090" s="52" t="s">
         <v>187</v>
@@ -55882,13 +55791,13 @@
         <v>27</v>
       </c>
       <c r="D2091" s="52" t="s">
-        <v>3216</v>
+        <v>3196</v>
       </c>
       <c r="E2091" s="52" t="s">
-        <v>3217</v>
+        <v>11</v>
       </c>
       <c r="F2091" s="52" t="s">
-        <v>3218</v>
+        <v>3197</v>
       </c>
       <c r="G2091" s="52" t="s">
         <v>83</v>
@@ -55905,10 +55814,10 @@
         <v>23</v>
       </c>
       <c r="E2092" s="52" t="s">
-        <v>3217</v>
+        <v>11</v>
       </c>
       <c r="F2092" s="52" t="s">
-        <v>3219</v>
+        <v>3198</v>
       </c>
       <c r="G2092" s="52"/>
     </row>
@@ -55923,10 +55832,10 @@
         <v>42</v>
       </c>
       <c r="E2093" s="52" t="s">
-        <v>3217</v>
+        <v>11</v>
       </c>
       <c r="F2093" s="52" t="s">
-        <v>3220</v>
+        <v>3199</v>
       </c>
       <c r="G2093" s="52" t="s">
         <v>83</v>
@@ -55937,16 +55846,16 @@
         <v>46289</v>
       </c>
       <c r="C2094" s="52" t="s">
-        <v>3221</v>
+        <v>3200</v>
       </c>
       <c r="D2094" s="52" t="s">
         <v>385</v>
       </c>
       <c r="E2094" s="52" t="s">
-        <v>3222</v>
+        <v>11</v>
       </c>
       <c r="F2094" s="52" t="s">
-        <v>3223</v>
+        <v>3201</v>
       </c>
       <c r="G2094" s="52" t="s">
         <v>51</v>
@@ -55963,10 +55872,10 @@
         <v>23</v>
       </c>
       <c r="E2095" s="52" t="s">
-        <v>3222</v>
+        <v>11</v>
       </c>
       <c r="F2095" s="52" t="s">
-        <v>3224</v>
+        <v>3202</v>
       </c>
       <c r="G2095" s="52" t="s">
         <v>54</v>
@@ -55983,10 +55892,10 @@
         <v>62</v>
       </c>
       <c r="E2096" s="52" t="s">
-        <v>3222</v>
+        <v>11</v>
       </c>
       <c r="F2096" s="52" t="s">
-        <v>3225</v>
+        <v>3203</v>
       </c>
       <c r="G2096" s="52" t="s">
         <v>64</v>
@@ -55997,16 +55906,16 @@
         <v>46289</v>
       </c>
       <c r="C2097" s="52" t="s">
-        <v>3226</v>
+        <v>3204</v>
       </c>
       <c r="D2097" s="52" t="s">
-        <v>3227</v>
+        <v>3205</v>
       </c>
       <c r="E2097" s="52" t="s">
-        <v>3222</v>
+        <v>11</v>
       </c>
       <c r="F2097" s="52" t="s">
-        <v>3228</v>
+        <v>3206</v>
       </c>
       <c r="G2097" s="52" t="s">
         <v>51</v>
@@ -56017,16 +55926,16 @@
         <v>46289</v>
       </c>
       <c r="C2098" s="52" t="s">
-        <v>3025</v>
+        <v>3013</v>
       </c>
       <c r="D2098" s="52" t="s">
         <v>385</v>
       </c>
       <c r="E2098" s="52" t="s">
-        <v>3222</v>
+        <v>11</v>
       </c>
       <c r="F2098" s="52" t="s">
-        <v>3229</v>
+        <v>3207</v>
       </c>
       <c r="G2098" s="52" t="s">
         <v>51</v>
@@ -56040,10 +55949,10 @@
         <v>2167</v>
       </c>
       <c r="D2099" s="52" t="s">
-        <v>3230</v>
+        <v>3208</v>
       </c>
       <c r="E2099" s="52" t="s">
-        <v>3222</v>
+        <v>11</v>
       </c>
       <c r="F2099" s="52" t="s">
         <v>1790</v>
@@ -56057,16 +55966,16 @@
         <v>46289</v>
       </c>
       <c r="C2100" s="52" t="s">
-        <v>3231</v>
+        <v>3209</v>
       </c>
       <c r="D2100" s="52" t="s">
-        <v>3232</v>
+        <v>3210</v>
       </c>
       <c r="E2100" s="52" t="s">
-        <v>3222</v>
+        <v>11</v>
       </c>
       <c r="F2100" s="52" t="s">
-        <v>3233</v>
+        <v>3211</v>
       </c>
       <c r="G2100" s="52" t="s">
         <v>51</v>
@@ -56077,16 +55986,16 @@
         <v>46289</v>
       </c>
       <c r="C2101" s="52" t="s">
-        <v>3231</v>
+        <v>3209</v>
       </c>
       <c r="D2101" s="52" t="s">
         <v>1860</v>
       </c>
       <c r="E2101" s="52" t="s">
-        <v>3222</v>
+        <v>11</v>
       </c>
       <c r="F2101" s="52" t="s">
-        <v>3234</v>
+        <v>3212</v>
       </c>
       <c r="G2101" s="52" t="s">
         <v>51</v>
@@ -56103,10 +56012,10 @@
         <v>62</v>
       </c>
       <c r="E2102" s="52" t="s">
-        <v>3222</v>
+        <v>11</v>
       </c>
       <c r="F2102" s="54" t="s">
-        <v>3235</v>
+        <v>3213</v>
       </c>
       <c r="G2102" s="54" t="s">
         <v>41</v>
@@ -56123,10 +56032,10 @@
         <v>385</v>
       </c>
       <c r="E2103" s="52" t="s">
-        <v>3222</v>
+        <v>11</v>
       </c>
       <c r="F2103" s="54" t="s">
-        <v>3236</v>
+        <v>3214</v>
       </c>
       <c r="G2103" s="54" t="s">
         <v>64</v>
@@ -56137,13 +56046,13 @@
         <v>46290</v>
       </c>
       <c r="C2104" s="54" t="s">
-        <v>3237</v>
+        <v>3215</v>
       </c>
       <c r="D2104" s="54" t="s">
         <v>859</v>
       </c>
       <c r="E2104" s="52" t="s">
-        <v>3238</v>
+        <v>11</v>
       </c>
       <c r="F2104" s="54" t="s">
         <v>135</v>
@@ -56157,16 +56066,16 @@
         <v>46290</v>
       </c>
       <c r="C2105" s="54" t="s">
-        <v>3239</v>
+        <v>3216</v>
       </c>
       <c r="D2105" s="54" t="s">
-        <v>3240</v>
+        <v>3217</v>
       </c>
       <c r="E2105" s="52" t="s">
-        <v>3238</v>
+        <v>11</v>
       </c>
       <c r="F2105" s="54" t="s">
-        <v>3241</v>
+        <v>3218</v>
       </c>
       <c r="G2105" s="54" t="s">
         <v>51</v>
@@ -56177,16 +56086,16 @@
         <v>46290</v>
       </c>
       <c r="C2106" s="54" t="s">
-        <v>3242</v>
+        <v>3219</v>
       </c>
       <c r="D2106" s="54" t="s">
         <v>52</v>
       </c>
       <c r="E2106" s="52" t="s">
-        <v>3238</v>
+        <v>11</v>
       </c>
       <c r="F2106" s="54" t="s">
-        <v>3243</v>
+        <v>3220</v>
       </c>
       <c r="G2106" s="54" t="s">
         <v>51</v>
@@ -56197,13 +56106,13 @@
         <v>46290</v>
       </c>
       <c r="C2107" s="54" t="s">
-        <v>2993</v>
+        <v>2983</v>
       </c>
       <c r="D2107" s="54" t="s">
         <v>1860</v>
       </c>
       <c r="E2107" s="52" t="s">
-        <v>3238</v>
+        <v>11</v>
       </c>
       <c r="F2107" s="54" t="s">
         <v>384</v>
@@ -56217,16 +56126,16 @@
         <v>46290</v>
       </c>
       <c r="C2108" s="54" t="s">
-        <v>3244</v>
+        <v>3221</v>
       </c>
       <c r="D2108" s="54" t="s">
         <v>385</v>
       </c>
       <c r="E2108" s="52" t="s">
-        <v>3238</v>
+        <v>11</v>
       </c>
       <c r="F2108" s="54" t="s">
-        <v>3245</v>
+        <v>3222</v>
       </c>
       <c r="G2108" s="54" t="s">
         <v>51</v>
@@ -56237,16 +56146,16 @@
         <v>46290</v>
       </c>
       <c r="C2109" s="54" t="s">
-        <v>3010</v>
+        <v>2999</v>
       </c>
       <c r="D2109" s="54" t="s">
         <v>94</v>
       </c>
       <c r="E2109" s="52" t="s">
-        <v>3238</v>
+        <v>11</v>
       </c>
       <c r="F2109" s="54" t="s">
-        <v>3246</v>
+        <v>3223</v>
       </c>
       <c r="G2109" s="54" t="s">
         <v>51</v>
@@ -56257,16 +56166,16 @@
         <v>46291</v>
       </c>
       <c r="C2110" s="52" t="s">
-        <v>3247</v>
+        <v>3224</v>
       </c>
       <c r="D2110" s="52" t="s">
         <v>207</v>
       </c>
       <c r="E2110" s="52" t="s">
-        <v>3248</v>
+        <v>11</v>
       </c>
       <c r="F2110" s="52" t="s">
-        <v>3249</v>
+        <v>3225</v>
       </c>
       <c r="G2110" s="52" t="s">
         <v>51</v>
@@ -56277,16 +56186,16 @@
         <v>46291</v>
       </c>
       <c r="C2111" s="52" t="s">
-        <v>3250</v>
+        <v>3226</v>
       </c>
       <c r="D2111" s="52" t="s">
         <v>1860</v>
       </c>
       <c r="E2111" s="52" t="s">
-        <v>3238</v>
+        <v>11</v>
       </c>
       <c r="F2111" s="52" t="s">
-        <v>3251</v>
+        <v>3227</v>
       </c>
       <c r="G2111" s="52" t="s">
         <v>51</v>
@@ -56297,16 +56206,16 @@
         <v>46291</v>
       </c>
       <c r="C2112" s="52" t="s">
-        <v>3252</v>
+        <v>3228</v>
       </c>
       <c r="D2112" s="52" t="s">
         <v>256</v>
       </c>
       <c r="E2112" s="52" t="s">
-        <v>3238</v>
+        <v>11</v>
       </c>
       <c r="F2112" s="52" t="s">
-        <v>3253</v>
+        <v>3229</v>
       </c>
       <c r="G2112" s="52" t="s">
         <v>51</v>
@@ -56317,16 +56226,16 @@
         <v>46291</v>
       </c>
       <c r="C2113" s="52" t="s">
-        <v>2987</v>
+        <v>2979</v>
       </c>
       <c r="D2113" s="52" t="s">
         <v>1662</v>
       </c>
       <c r="E2113" s="52" t="s">
-        <v>3238</v>
+        <v>11</v>
       </c>
       <c r="F2113" s="52" t="s">
-        <v>3254</v>
+        <v>3230</v>
       </c>
       <c r="G2113" s="52" t="s">
         <v>51</v>
@@ -56343,10 +56252,10 @@
         <v>42</v>
       </c>
       <c r="E2114" s="52" t="s">
-        <v>3255</v>
+        <v>28</v>
       </c>
       <c r="F2114" s="52" t="s">
-        <v>3256</v>
+        <v>3231</v>
       </c>
       <c r="G2114" s="52" t="s">
         <v>51</v>
@@ -56357,13 +56266,13 @@
         <v>46291</v>
       </c>
       <c r="C2115" s="52" t="s">
-        <v>3247</v>
+        <v>3224</v>
       </c>
       <c r="D2115" s="52" t="s">
         <v>94</v>
       </c>
       <c r="E2115" s="52" t="s">
-        <v>3255</v>
+        <v>28</v>
       </c>
       <c r="F2115" s="52" t="s">
         <v>2309</v>
@@ -56383,7 +56292,7 @@
         <v>15</v>
       </c>
       <c r="E2116" s="52" t="s">
-        <v>3255</v>
+        <v>28</v>
       </c>
       <c r="F2116" s="52" t="s">
         <v>2214</v>
@@ -56403,10 +56312,10 @@
         <v>32</v>
       </c>
       <c r="E2117" s="52" t="s">
-        <v>3255</v>
+        <v>28</v>
       </c>
       <c r="F2117" s="52" t="s">
-        <v>3257</v>
+        <v>3232</v>
       </c>
       <c r="G2117" s="52" t="s">
         <v>34</v>
@@ -56417,13 +56326,13 @@
         <v>46291</v>
       </c>
       <c r="C2118" s="52" t="s">
-        <v>3258</v>
+        <v>3233</v>
       </c>
       <c r="D2118" s="52" t="s">
         <v>19</v>
       </c>
       <c r="E2118" s="52" t="s">
-        <v>3255</v>
+        <v>28</v>
       </c>
       <c r="F2118" s="52" t="s">
         <v>442</v>
@@ -56437,16 +56346,16 @@
         <v>46291</v>
       </c>
       <c r="C2119" s="52" t="s">
-        <v>3198</v>
+        <v>3179</v>
       </c>
       <c r="D2119" s="52" t="s">
         <v>1070</v>
       </c>
       <c r="E2119" s="52" t="s">
-        <v>3255</v>
+        <v>28</v>
       </c>
       <c r="F2119" s="52" t="s">
-        <v>3259</v>
+        <v>3234</v>
       </c>
       <c r="G2119" s="52" t="s">
         <v>34</v>
@@ -56463,7 +56372,7 @@
         <v>202</v>
       </c>
       <c r="E2120" s="52" t="s">
-        <v>3255</v>
+        <v>28</v>
       </c>
       <c r="F2120" s="52" t="s">
         <v>399</v>
@@ -56483,10 +56392,10 @@
         <v>44</v>
       </c>
       <c r="E2121" s="52" t="s">
-        <v>3255</v>
+        <v>28</v>
       </c>
       <c r="F2121" s="52" t="s">
-        <v>3260</v>
+        <v>3235</v>
       </c>
       <c r="G2121" s="52" t="s">
         <v>70</v>
@@ -56503,10 +56412,10 @@
         <v>42</v>
       </c>
       <c r="E2122" s="52" t="s">
-        <v>3255</v>
+        <v>28</v>
       </c>
       <c r="F2122" s="52" t="s">
-        <v>3261</v>
+        <v>3236</v>
       </c>
       <c r="G2122" s="52" t="s">
         <v>34</v>
@@ -56517,13 +56426,13 @@
         <v>46291</v>
       </c>
       <c r="C2123" s="52" t="s">
-        <v>3258</v>
+        <v>3233</v>
       </c>
       <c r="D2123" s="52" t="s">
         <v>389</v>
       </c>
       <c r="E2123" s="52" t="s">
-        <v>3255</v>
+        <v>28</v>
       </c>
       <c r="F2123" s="52" t="s">
         <v>372</v>
@@ -56543,10 +56452,10 @@
         <v>44</v>
       </c>
       <c r="E2124" s="52" t="s">
-        <v>3255</v>
+        <v>28</v>
       </c>
       <c r="F2124" s="52" t="s">
-        <v>3262</v>
+        <v>3237</v>
       </c>
       <c r="G2124" s="52" t="s">
         <v>371</v>
@@ -56563,10 +56472,10 @@
         <v>44</v>
       </c>
       <c r="E2125" s="52" t="s">
-        <v>3255</v>
+        <v>28</v>
       </c>
       <c r="F2125" s="52" t="s">
-        <v>3263</v>
+        <v>3238</v>
       </c>
       <c r="G2125" s="52" t="s">
         <v>70</v>
@@ -56583,10 +56492,10 @@
         <v>44</v>
       </c>
       <c r="E2126" s="52" t="s">
-        <v>3255</v>
+        <v>28</v>
       </c>
       <c r="F2126" s="52" t="s">
-        <v>3264</v>
+        <v>3239</v>
       </c>
       <c r="G2126" s="52" t="s">
         <v>70</v>
@@ -56603,10 +56512,10 @@
         <v>23</v>
       </c>
       <c r="E2127" s="52" t="s">
-        <v>3255</v>
+        <v>28</v>
       </c>
       <c r="F2127" s="52" t="s">
-        <v>3265</v>
+        <v>3240</v>
       </c>
       <c r="G2127" s="52" t="s">
         <v>30</v>
@@ -56617,16 +56526,16 @@
         <v>46291</v>
       </c>
       <c r="C2128" s="52" t="s">
-        <v>3196</v>
+        <v>3177</v>
       </c>
       <c r="D2128" s="52" t="s">
         <v>76</v>
       </c>
       <c r="E2128" s="52" t="s">
-        <v>3255</v>
+        <v>28</v>
       </c>
       <c r="F2128" s="52" t="s">
-        <v>3266</v>
+        <v>3241</v>
       </c>
       <c r="G2128" s="52" t="s">
         <v>34</v>
@@ -56643,10 +56552,10 @@
         <v>44</v>
       </c>
       <c r="E2129" s="52" t="s">
-        <v>3255</v>
+        <v>28</v>
       </c>
       <c r="F2129" s="52" t="s">
-        <v>3267</v>
+        <v>3242</v>
       </c>
       <c r="G2129" s="52" t="s">
         <v>34</v>
@@ -56657,16 +56566,16 @@
         <v>46291</v>
       </c>
       <c r="C2130" s="52" t="s">
-        <v>3198</v>
+        <v>3179</v>
       </c>
       <c r="D2130" s="52" t="s">
         <v>42</v>
       </c>
       <c r="E2130" s="52" t="s">
-        <v>3255</v>
+        <v>28</v>
       </c>
       <c r="F2130" s="52" t="s">
-        <v>3268</v>
+        <v>3243</v>
       </c>
       <c r="G2130" s="52" t="s">
         <v>34</v>
@@ -56683,7 +56592,7 @@
         <v>42</v>
       </c>
       <c r="E2131" s="52" t="s">
-        <v>3255</v>
+        <v>28</v>
       </c>
       <c r="F2131" s="52" t="s">
         <v>372</v>
@@ -56697,16 +56606,16 @@
         <v>46291</v>
       </c>
       <c r="C2132" s="52" t="s">
-        <v>2958</v>
+        <v>2952</v>
       </c>
       <c r="D2132" s="52" t="s">
         <v>19</v>
       </c>
       <c r="E2132" s="52" t="s">
-        <v>3269</v>
+        <v>11</v>
       </c>
       <c r="F2132" s="53" t="s">
-        <v>3270</v>
+        <v>3244</v>
       </c>
       <c r="G2132" s="52" t="s">
         <v>187</v>
@@ -56717,16 +56626,16 @@
         <v>46291</v>
       </c>
       <c r="C2133" s="52" t="s">
-        <v>3042</v>
+        <v>3030</v>
       </c>
       <c r="D2133" s="52" t="s">
-        <v>3271</v>
+        <v>3245</v>
       </c>
       <c r="E2133" s="52" t="s">
-        <v>3269</v>
+        <v>11</v>
       </c>
       <c r="F2133" s="52" t="s">
-        <v>3272</v>
+        <v>3246</v>
       </c>
       <c r="G2133" s="52" t="s">
         <v>30</v>
@@ -56743,7 +56652,7 @@
         <v>44</v>
       </c>
       <c r="E2134" s="52" t="s">
-        <v>3269</v>
+        <v>11</v>
       </c>
       <c r="F2134" s="52" t="s">
         <v>2192</v>
@@ -56763,10 +56672,10 @@
         <v>44</v>
       </c>
       <c r="E2135" s="52" t="s">
-        <v>3273</v>
+        <v>28</v>
       </c>
       <c r="F2135" s="52" t="s">
-        <v>3274</v>
+        <v>3247</v>
       </c>
       <c r="G2135" s="52" t="s">
         <v>34</v>
@@ -56783,10 +56692,10 @@
         <v>403</v>
       </c>
       <c r="E2136" s="52" t="s">
-        <v>3273</v>
+        <v>28</v>
       </c>
       <c r="F2136" s="52" t="s">
-        <v>3275</v>
+        <v>3248</v>
       </c>
       <c r="G2136" s="52" t="s">
         <v>70</v>
@@ -56803,10 +56712,10 @@
         <v>922</v>
       </c>
       <c r="E2137" s="52" t="s">
-        <v>3273</v>
+        <v>28</v>
       </c>
       <c r="F2137" s="52" t="s">
-        <v>3276</v>
+        <v>3249</v>
       </c>
       <c r="G2137" s="52" t="s">
         <v>34</v>
@@ -56823,7 +56732,7 @@
         <v>1991</v>
       </c>
       <c r="E2138" s="52" t="s">
-        <v>3273</v>
+        <v>28</v>
       </c>
       <c r="F2138" s="52" t="s">
         <v>442</v>
@@ -56843,10 +56752,10 @@
         <v>1591</v>
       </c>
       <c r="E2139" s="52" t="s">
-        <v>3273</v>
+        <v>28</v>
       </c>
       <c r="F2139" s="52" t="s">
-        <v>3277</v>
+        <v>3250</v>
       </c>
       <c r="G2139" s="52" t="s">
         <v>34</v>
@@ -56863,10 +56772,10 @@
         <v>15</v>
       </c>
       <c r="E2140" s="52" t="s">
-        <v>3273</v>
+        <v>28</v>
       </c>
       <c r="F2140" s="52" t="s">
-        <v>3278</v>
+        <v>3251</v>
       </c>
       <c r="G2140" s="52" t="s">
         <v>30</v>
@@ -56883,10 +56792,10 @@
         <v>44</v>
       </c>
       <c r="E2141" s="52" t="s">
-        <v>3273</v>
+        <v>28</v>
       </c>
       <c r="F2141" s="52" t="s">
-        <v>3279</v>
+        <v>3252</v>
       </c>
       <c r="G2141" s="52" t="s">
         <v>34</v>
@@ -56903,10 +56812,10 @@
         <v>44</v>
       </c>
       <c r="E2142" s="52" t="s">
-        <v>3273</v>
+        <v>28</v>
       </c>
       <c r="F2142" s="52" t="s">
-        <v>3280</v>
+        <v>3253</v>
       </c>
       <c r="G2142" s="52" t="s">
         <v>70</v>
@@ -56923,10 +56832,10 @@
         <v>509</v>
       </c>
       <c r="E2143" s="52" t="s">
-        <v>3273</v>
+        <v>28</v>
       </c>
       <c r="F2143" s="52" t="s">
-        <v>3281</v>
+        <v>3254</v>
       </c>
       <c r="G2143" s="52" t="s">
         <v>34</v>
@@ -56937,16 +56846,16 @@
         <v>46292</v>
       </c>
       <c r="C2144" s="52" t="s">
-        <v>3282</v>
+        <v>3255</v>
       </c>
       <c r="D2144" s="52" t="s">
         <v>44</v>
       </c>
       <c r="E2144" s="52" t="s">
-        <v>3273</v>
+        <v>28</v>
       </c>
       <c r="F2144" s="52" t="s">
-        <v>3283</v>
+        <v>3256</v>
       </c>
       <c r="G2144" s="52" t="s">
         <v>70</v>
@@ -56963,10 +56872,10 @@
         <v>42</v>
       </c>
       <c r="E2145" s="52" t="s">
-        <v>3273</v>
+        <v>28</v>
       </c>
       <c r="F2145" s="52" t="s">
-        <v>3284</v>
+        <v>3257</v>
       </c>
       <c r="G2145" s="52" t="s">
         <v>34</v>
@@ -56980,13 +56889,13 @@
         <v>1904</v>
       </c>
       <c r="D2146" s="52" t="s">
-        <v>3285</v>
+        <v>3258</v>
       </c>
       <c r="E2146" s="52" t="s">
-        <v>3273</v>
+        <v>28</v>
       </c>
       <c r="F2146" s="52" t="s">
-        <v>3286</v>
+        <v>3259</v>
       </c>
       <c r="G2146" s="52" t="s">
         <v>34</v>
@@ -57003,7 +56912,7 @@
         <v>374</v>
       </c>
       <c r="E2147" s="52" t="s">
-        <v>3273</v>
+        <v>28</v>
       </c>
       <c r="F2147" s="52" t="s">
         <v>508</v>
@@ -57017,16 +56926,16 @@
         <v>46292</v>
       </c>
       <c r="C2148" s="52" t="s">
-        <v>3287</v>
+        <v>3260</v>
       </c>
       <c r="D2148" s="52" t="s">
         <v>62</v>
       </c>
       <c r="E2148" s="52" t="s">
-        <v>3288</v>
+        <v>11</v>
       </c>
       <c r="F2148" s="42" t="s">
-        <v>3289</v>
+        <v>3261</v>
       </c>
       <c r="G2148" s="52" t="s">
         <v>70</v>
@@ -57037,16 +56946,16 @@
         <v>46292</v>
       </c>
       <c r="C2149" s="52" t="s">
-        <v>3290</v>
+        <v>3262</v>
       </c>
       <c r="D2149" s="52" t="s">
         <v>385</v>
       </c>
       <c r="E2149" s="52" t="s">
-        <v>3288</v>
+        <v>11</v>
       </c>
       <c r="F2149" s="42" t="s">
-        <v>3291</v>
+        <v>3263</v>
       </c>
       <c r="G2149" s="52" t="s">
         <v>70</v>
@@ -57057,16 +56966,16 @@
         <v>46292</v>
       </c>
       <c r="C2150" s="52" t="s">
-        <v>3292</v>
+        <v>3264</v>
       </c>
       <c r="D2150" s="52" t="s">
         <v>44</v>
       </c>
       <c r="E2150" s="52" t="s">
-        <v>3288</v>
+        <v>11</v>
       </c>
       <c r="F2150" s="42" t="s">
-        <v>3293</v>
+        <v>3265</v>
       </c>
       <c r="G2150" s="52" t="s">
         <v>70</v>
@@ -57077,16 +56986,16 @@
         <v>46292</v>
       </c>
       <c r="C2151" s="52" t="s">
-        <v>3294</v>
+        <v>3266</v>
       </c>
       <c r="D2151" s="52" t="s">
         <v>44</v>
       </c>
       <c r="E2151" s="52" t="s">
-        <v>3288</v>
+        <v>11</v>
       </c>
       <c r="F2151" s="52" t="s">
-        <v>3295</v>
+        <v>3267</v>
       </c>
       <c r="G2151" s="52" t="s">
         <v>70</v>
@@ -57097,16 +57006,16 @@
         <v>46292</v>
       </c>
       <c r="C2152" s="52" t="s">
-        <v>3296</v>
+        <v>3268</v>
       </c>
       <c r="D2152" s="52" t="s">
         <v>1591</v>
       </c>
       <c r="E2152" s="52" t="s">
-        <v>3288</v>
+        <v>11</v>
       </c>
       <c r="F2152" s="52" t="s">
-        <v>3297</v>
+        <v>3269</v>
       </c>
       <c r="G2152" s="52" t="s">
         <v>30</v>
@@ -57117,16 +57026,16 @@
         <v>46293</v>
       </c>
       <c r="C2153" s="52" t="s">
-        <v>3298</v>
+        <v>3270</v>
       </c>
       <c r="D2153" s="52" t="s">
         <v>15</v>
       </c>
       <c r="E2153" s="52" t="s">
-        <v>3288</v>
+        <v>11</v>
       </c>
       <c r="F2153" s="52" t="s">
-        <v>3299</v>
+        <v>3271</v>
       </c>
       <c r="G2153" s="52" t="s">
         <v>187</v>
@@ -57143,7 +57052,7 @@
         <v>52</v>
       </c>
       <c r="E2154" s="52" t="s">
-        <v>3288</v>
+        <v>11</v>
       </c>
       <c r="F2154" s="52" t="s">
         <v>1597</v>
@@ -57160,13 +57069,13 @@
         <v>2142</v>
       </c>
       <c r="D2155" s="52" t="s">
-        <v>3300</v>
+        <v>3272</v>
       </c>
       <c r="E2155" s="52" t="s">
-        <v>3288</v>
+        <v>11</v>
       </c>
       <c r="F2155" s="52" t="s">
-        <v>3301</v>
+        <v>3273</v>
       </c>
       <c r="G2155" s="52" t="s">
         <v>30</v>
@@ -57177,16 +57086,16 @@
         <v>46293</v>
       </c>
       <c r="C2156" s="52" t="s">
-        <v>3302</v>
+        <v>3274</v>
       </c>
       <c r="D2156" s="52" t="s">
-        <v>3303</v>
+        <v>3275</v>
       </c>
       <c r="E2156" s="52" t="s">
-        <v>3288</v>
+        <v>11</v>
       </c>
       <c r="F2156" s="52" t="s">
-        <v>3304</v>
+        <v>3276</v>
       </c>
       <c r="G2156" s="52" t="s">
         <v>187</v>
@@ -57203,10 +57112,10 @@
         <v>1935</v>
       </c>
       <c r="E2157" s="52" t="s">
-        <v>3305</v>
+        <v>11</v>
       </c>
       <c r="F2157" s="52" t="s">
-        <v>3306</v>
+        <v>3277</v>
       </c>
       <c r="G2157" s="52" t="s">
         <v>51</v>
@@ -57217,16 +57126,16 @@
         <v>46293</v>
       </c>
       <c r="C2158" s="52" t="s">
-        <v>3247</v>
+        <v>3224</v>
       </c>
       <c r="D2158" s="52" t="s">
         <v>23</v>
       </c>
       <c r="E2158" s="52" t="s">
-        <v>3305</v>
+        <v>11</v>
       </c>
       <c r="F2158" s="52" t="s">
-        <v>3307</v>
+        <v>3278</v>
       </c>
       <c r="G2158" s="52" t="s">
         <v>51</v>
@@ -57237,16 +57146,16 @@
         <v>46294</v>
       </c>
       <c r="C2159" s="52" t="s">
-        <v>3308</v>
+        <v>3279</v>
       </c>
       <c r="D2159" s="52" t="s">
         <v>1687</v>
       </c>
       <c r="E2159" s="52" t="s">
-        <v>3305</v>
+        <v>11</v>
       </c>
       <c r="F2159" s="52" t="s">
-        <v>3309</v>
+        <v>3280</v>
       </c>
       <c r="G2159" s="52" t="s">
         <v>51</v>
@@ -57257,16 +57166,16 @@
         <v>46294</v>
       </c>
       <c r="C2160" s="52" t="s">
-        <v>3310</v>
+        <v>3281</v>
       </c>
       <c r="D2160" s="52" t="s">
         <v>52</v>
       </c>
       <c r="E2160" s="52" t="s">
-        <v>3305</v>
+        <v>11</v>
       </c>
       <c r="F2160" s="52" t="s">
-        <v>3311</v>
+        <v>3282</v>
       </c>
       <c r="G2160" s="52" t="s">
         <v>51</v>
@@ -57277,16 +57186,16 @@
         <v>46294</v>
       </c>
       <c r="C2161" s="52" t="s">
-        <v>3312</v>
+        <v>3283</v>
       </c>
       <c r="D2161" s="52" t="s">
         <v>52</v>
       </c>
       <c r="E2161" s="52" t="s">
-        <v>3305</v>
+        <v>11</v>
       </c>
       <c r="F2161" s="52" t="s">
-        <v>3313</v>
+        <v>3284</v>
       </c>
       <c r="G2161" s="52" t="s">
         <v>51</v>
@@ -57297,16 +57206,16 @@
         <v>46294</v>
       </c>
       <c r="C2162" s="52" t="s">
-        <v>3314</v>
+        <v>3285</v>
       </c>
       <c r="D2162" s="52" t="s">
         <v>570</v>
       </c>
       <c r="E2162" s="52" t="s">
-        <v>3305</v>
+        <v>11</v>
       </c>
       <c r="F2162" s="52" t="s">
-        <v>3315</v>
+        <v>3286</v>
       </c>
       <c r="G2162" s="52" t="s">
         <v>51</v>
@@ -57317,16 +57226,16 @@
         <v>46294</v>
       </c>
       <c r="C2163" s="52" t="s">
-        <v>3042</v>
+        <v>3030</v>
       </c>
       <c r="D2163" s="52" t="s">
         <v>52</v>
       </c>
       <c r="E2163" s="52" t="s">
-        <v>2907</v>
+        <v>11</v>
       </c>
       <c r="F2163" s="52" t="s">
-        <v>3316</v>
+        <v>3287</v>
       </c>
       <c r="G2163" s="52" t="s">
         <v>51</v>
@@ -57337,16 +57246,16 @@
         <v>46294</v>
       </c>
       <c r="C2164" s="52" t="s">
-        <v>3317</v>
+        <v>3288</v>
       </c>
       <c r="D2164" s="52" t="s">
         <v>23</v>
       </c>
       <c r="E2164" s="52" t="s">
-        <v>2907</v>
+        <v>11</v>
       </c>
       <c r="F2164" s="52" t="s">
-        <v>3318</v>
+        <v>3289</v>
       </c>
       <c r="G2164" s="52" t="s">
         <v>51</v>
@@ -57363,10 +57272,10 @@
         <v>385</v>
       </c>
       <c r="E2165" s="52" t="s">
-        <v>2907</v>
+        <v>11</v>
       </c>
       <c r="F2165" s="52" t="s">
-        <v>3319</v>
+        <v>3290</v>
       </c>
       <c r="G2165" s="52" t="s">
         <v>64</v>
@@ -57383,10 +57292,10 @@
         <v>570</v>
       </c>
       <c r="E2166" s="52" t="s">
-        <v>2907</v>
+        <v>11</v>
       </c>
       <c r="F2166" s="52" t="s">
-        <v>3320</v>
+        <v>3291</v>
       </c>
       <c r="G2166" s="52" t="s">
         <v>87</v>
@@ -57403,10 +57312,10 @@
         <v>385</v>
       </c>
       <c r="E2167" s="52" t="s">
-        <v>2907</v>
+        <v>11</v>
       </c>
       <c r="F2167" s="52" t="s">
-        <v>3321</v>
+        <v>3292</v>
       </c>
       <c r="G2167" s="52" t="s">
         <v>41</v>
@@ -57423,10 +57332,10 @@
         <v>385</v>
       </c>
       <c r="E2168" s="52" t="s">
-        <v>2907</v>
+        <v>11</v>
       </c>
       <c r="F2168" s="52" t="s">
-        <v>3322</v>
+        <v>3293</v>
       </c>
       <c r="G2168" s="52" t="s">
         <v>64</v>
@@ -57437,16 +57346,16 @@
         <v>46294</v>
       </c>
       <c r="C2169" s="52" t="s">
-        <v>3323</v>
+        <v>3294</v>
       </c>
       <c r="D2169" s="52" t="s">
         <v>52</v>
       </c>
       <c r="E2169" s="52" t="s">
-        <v>2907</v>
+        <v>11</v>
       </c>
       <c r="F2169" s="52" t="s">
-        <v>3324</v>
+        <v>3295</v>
       </c>
       <c r="G2169" s="52" t="s">
         <v>51</v>
@@ -57457,13 +57366,13 @@
         <v>46294</v>
       </c>
       <c r="C2170" s="52" t="s">
-        <v>3325</v>
+        <v>3296</v>
       </c>
       <c r="D2170" s="52" t="s">
         <v>456</v>
       </c>
       <c r="E2170" s="52" t="s">
-        <v>2907</v>
+        <v>11</v>
       </c>
       <c r="F2170" s="52" t="s">
         <v>2277</v>
@@ -57483,10 +57392,10 @@
         <v>256</v>
       </c>
       <c r="E2171" s="52" t="s">
-        <v>2907</v>
+        <v>11</v>
       </c>
       <c r="F2171" s="52" t="s">
-        <v>3326</v>
+        <v>3297</v>
       </c>
       <c r="G2171" s="52" t="s">
         <v>64</v>
@@ -57503,10 +57412,10 @@
         <v>741</v>
       </c>
       <c r="E2172" s="52" t="s">
-        <v>2907</v>
+        <v>11</v>
       </c>
       <c r="F2172" s="52" t="s">
-        <v>3327</v>
+        <v>3298</v>
       </c>
       <c r="G2172" s="52" t="s">
         <v>64</v>
@@ -57517,13 +57426,13 @@
         <v>46295</v>
       </c>
       <c r="C2173" s="52" t="s">
-        <v>3328</v>
+        <v>3299</v>
       </c>
       <c r="D2173" s="52" t="s">
         <v>570</v>
       </c>
       <c r="E2173" s="52" t="s">
-        <v>2907</v>
+        <v>11</v>
       </c>
       <c r="F2173" s="52" t="s">
         <v>1191</v>
@@ -57537,16 +57446,16 @@
         <v>46295</v>
       </c>
       <c r="C2174" s="52" t="s">
-        <v>3329</v>
+        <v>3300</v>
       </c>
       <c r="D2174" s="52" t="s">
         <v>278</v>
       </c>
       <c r="E2174" s="52" t="s">
-        <v>2907</v>
+        <v>11</v>
       </c>
       <c r="F2174" s="52" t="s">
-        <v>3330</v>
+        <v>3301</v>
       </c>
       <c r="G2174" s="52" t="s">
         <v>64</v>
@@ -57558,7 +57467,9 @@
       </c>
       <c r="C2175" s="52"/>
       <c r="D2175" s="52"/>
-      <c r="E2175" s="52"/>
+      <c r="E2175" s="52" t="s">
+        <v>11</v>
+      </c>
       <c r="F2175" s="52"/>
       <c r="G2175" s="52"/>
     </row>
@@ -57572,11 +57483,11 @@
       <c r="D2176" s="52" t="s">
         <v>42</v>
       </c>
-      <c r="E2176" s="73" t="s">
-        <v>3331</v>
+      <c r="E2176" s="52" t="s">
+        <v>11</v>
       </c>
       <c r="F2176" s="52" t="s">
-        <v>3332</v>
+        <v>3302</v>
       </c>
       <c r="G2176" s="52" t="s">
         <v>92</v>
@@ -57590,13 +57501,13 @@
         <v>176</v>
       </c>
       <c r="D2177" s="52" t="s">
-        <v>3333</v>
-      </c>
-      <c r="E2177" s="73" t="s">
-        <v>3331</v>
+        <v>3303</v>
+      </c>
+      <c r="E2177" s="52" t="s">
+        <v>11</v>
       </c>
       <c r="F2177" s="52" t="s">
-        <v>3334</v>
+        <v>3304</v>
       </c>
       <c r="G2177" s="52" t="s">
         <v>92</v>
@@ -57612,11 +57523,11 @@
       <c r="D2178" s="52" t="s">
         <v>741</v>
       </c>
-      <c r="E2178" s="73" t="s">
-        <v>3331</v>
+      <c r="E2178" s="52" t="s">
+        <v>11</v>
       </c>
       <c r="F2178" s="52" t="s">
-        <v>3334</v>
+        <v>3304</v>
       </c>
       <c r="G2178" s="52" t="s">
         <v>92</v>
@@ -57632,11 +57543,11 @@
       <c r="D2179" s="52" t="s">
         <v>741</v>
       </c>
-      <c r="E2179" s="73" t="s">
-        <v>3331</v>
+      <c r="E2179" s="52" t="s">
+        <v>11</v>
       </c>
       <c r="F2179" s="52" t="s">
-        <v>3334</v>
+        <v>3304</v>
       </c>
       <c r="G2179" s="52" t="s">
         <v>92</v>
@@ -57652,11 +57563,11 @@
       <c r="D2180" s="52" t="s">
         <v>741</v>
       </c>
-      <c r="E2180" s="73" t="s">
-        <v>3331</v>
+      <c r="E2180" s="52" t="s">
+        <v>11</v>
       </c>
       <c r="F2180" s="52" t="s">
-        <v>3335</v>
+        <v>3305</v>
       </c>
       <c r="G2180" s="52" t="s">
         <v>92</v>
@@ -57672,14 +57583,14 @@
       <c r="D2181" s="52" t="s">
         <v>42</v>
       </c>
-      <c r="E2181" s="73" t="s">
-        <v>3331</v>
+      <c r="E2181" s="52" t="s">
+        <v>11</v>
       </c>
       <c r="F2181" s="52" t="s">
-        <v>3336</v>
+        <v>3306</v>
       </c>
       <c r="G2181" s="52" t="s">
-        <v>3337</v>
+        <v>3307</v>
       </c>
     </row>
     <row r="2182" spans="2:7" ht="15" customHeight="1">
@@ -57687,16 +57598,16 @@
         <v>46295</v>
       </c>
       <c r="C2182" s="52" t="s">
-        <v>3338</v>
+        <v>3308</v>
       </c>
       <c r="D2182" s="52" t="s">
         <v>42</v>
       </c>
-      <c r="E2182" s="73" t="s">
-        <v>3331</v>
+      <c r="E2182" s="52" t="s">
+        <v>11</v>
       </c>
       <c r="F2182" s="53" t="s">
-        <v>3339</v>
+        <v>3309</v>
       </c>
       <c r="G2182" s="52" t="s">
         <v>92</v>
